--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -111,8 +111,14 @@
       <color rgb="001A1A1A"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="002E7D32"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -209,8 +215,13 @@
         <fgColor rgb="00F5F5F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B08F36"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -335,11 +346,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -575,6 +600,12 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -809,13 +840,13 @@
 (직접 입력)</t>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0" shapeId="0">
+    <comment ref="T4" authorId="0" shapeId="0">
       <text>
         <t>▣ 상태
 (직접 입력)</t>
       </text>
     </comment>
-    <comment ref="R4" authorId="0" shapeId="0">
+    <comment ref="U4" authorId="0" shapeId="0">
       <text>
         <t>▣ 메모
 (직접 입력)</t>
@@ -1115,7 +1146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R57"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1134,8 +1165,9 @@
     <col width="9" customWidth="1" style="68" min="14" max="14"/>
     <col width="12" customWidth="1" style="68" min="15" max="15"/>
     <col width="8" customWidth="1" style="68" min="16" max="16"/>
-    <col width="10" customWidth="1" style="68" min="17" max="17"/>
-    <col width="28" customWidth="1" style="68" min="18" max="18"/>
+    <col width="12" customWidth="1" style="68" min="17" max="17"/>
+    <col width="12" customWidth="1" style="68" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1159,8 +1191,8 @@
       <c r="N1" s="46" t="n"/>
       <c r="O1" s="46" t="n"/>
       <c r="P1" s="46" t="n"/>
-      <c r="Q1" s="46" t="n"/>
-      <c r="R1" s="47" t="n"/>
+      <c r="T1" s="46" t="n"/>
+      <c r="U1" s="47" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="76" t="inlineStr">
@@ -1183,8 +1215,8 @@
       <c r="N2" s="46" t="n"/>
       <c r="O2" s="46" t="n"/>
       <c r="P2" s="46" t="n"/>
-      <c r="Q2" s="47" t="n"/>
-      <c r="R2" s="77" t="inlineStr">
+      <c r="T2" s="47" t="n"/>
+      <c r="U2" s="77" t="inlineStr">
         <is>
           <t>업데이트: 2026-05-02 01:42</t>
         </is>
@@ -1271,12 +1303,27 @@
           <t>✏입력</t>
         </is>
       </c>
-      <c r="Q3" s="28" t="inlineStr">
+      <c r="Q3" s="78" t="inlineStr">
+        <is>
+          <t>✏입력</t>
+        </is>
+      </c>
+      <c r="R3" s="78" t="inlineStr">
+        <is>
+          <t>✏입력</t>
+        </is>
+      </c>
+      <c r="S3" s="78" t="inlineStr">
+        <is>
+          <t>✏입력</t>
+        </is>
+      </c>
+      <c r="T3" s="28" t="inlineStr">
         <is>
           <t>✏선택▼</t>
         </is>
       </c>
-      <c r="R3" s="29" t="inlineStr">
+      <c r="U3" s="29" t="inlineStr">
         <is>
           <t>✏메모</t>
         </is>
@@ -1363,12 +1410,30 @@
           <t>메뉴얼</t>
         </is>
       </c>
-      <c r="Q4" s="32" t="inlineStr">
+      <c r="Q4" s="79" t="inlineStr">
+        <is>
+          <t>제안서
+완료일</t>
+        </is>
+      </c>
+      <c r="R4" s="79" t="inlineStr">
+        <is>
+          <t>설계
+완료일</t>
+        </is>
+      </c>
+      <c r="S4" s="79" t="inlineStr">
+        <is>
+          <t>가공의뢰
+입고일</t>
+        </is>
+      </c>
+      <c r="T4" s="32" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="R4" s="32" t="inlineStr">
+      <c r="U4" s="32" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1441,12 +1506,12 @@
       <c r="P5" s="37" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q5" s="35" t="inlineStr">
+      <c r="T5" s="35" t="inlineStr">
         <is>
           <t>진행중</t>
         </is>
       </c>
-      <c r="R5" s="38" t="n"/>
+      <c r="U5" s="38" t="n"/>
     </row>
     <row r="6" ht="22.05" customHeight="1">
       <c r="A6" s="39" t="n">
@@ -1511,12 +1576,12 @@
       <c r="P6" s="43" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q6" s="41" t="inlineStr">
+      <c r="T6" s="41" t="inlineStr">
         <is>
           <t>진행중</t>
         </is>
       </c>
-      <c r="R6" s="44" t="n"/>
+      <c r="U6" s="44" t="n"/>
     </row>
     <row r="7" ht="22.05" customHeight="1">
       <c r="A7" s="33" t="n">
@@ -1579,12 +1644,12 @@
       <c r="P7" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" s="35" t="inlineStr">
+      <c r="T7" s="35" t="inlineStr">
         <is>
           <t>진행중</t>
         </is>
       </c>
-      <c r="R7" s="38" t="n"/>
+      <c r="U7" s="38" t="n"/>
     </row>
     <row r="8" ht="22.05" customHeight="1">
       <c r="A8" s="39" t="n">
@@ -1637,8 +1702,8 @@
       <c r="N8" s="43" t="n"/>
       <c r="O8" s="43" t="n"/>
       <c r="P8" s="43" t="n"/>
-      <c r="Q8" s="41" t="n"/>
-      <c r="R8" s="44" t="n"/>
+      <c r="T8" s="41" t="n"/>
+      <c r="U8" s="44" t="n"/>
     </row>
     <row r="9" ht="22.05" customHeight="1">
       <c r="A9" s="33" t="n">
@@ -1691,8 +1756,8 @@
       <c r="N9" s="37" t="n"/>
       <c r="O9" s="37" t="n"/>
       <c r="P9" s="37" t="n"/>
-      <c r="Q9" s="35" t="n"/>
-      <c r="R9" s="38" t="n"/>
+      <c r="T9" s="35" t="n"/>
+      <c r="U9" s="38" t="n"/>
     </row>
     <row r="10" ht="22.05" customHeight="1">
       <c r="A10" s="39" t="n">
@@ -1745,8 +1810,8 @@
       <c r="N10" s="43" t="n"/>
       <c r="O10" s="43" t="n"/>
       <c r="P10" s="43" t="n"/>
-      <c r="Q10" s="41" t="n"/>
-      <c r="R10" s="44" t="n"/>
+      <c r="T10" s="41" t="n"/>
+      <c r="U10" s="44" t="n"/>
     </row>
     <row r="11" ht="22.05" customHeight="1">
       <c r="A11" s="33" t="n">
@@ -1799,8 +1864,8 @@
       <c r="N11" s="37" t="n"/>
       <c r="O11" s="37" t="n"/>
       <c r="P11" s="37" t="n"/>
-      <c r="Q11" s="35" t="n"/>
-      <c r="R11" s="38" t="n"/>
+      <c r="T11" s="35" t="n"/>
+      <c r="U11" s="38" t="n"/>
     </row>
     <row r="12" ht="22.05" customHeight="1">
       <c r="A12" s="39" t="n">
@@ -1853,8 +1918,8 @@
       <c r="N12" s="43" t="n"/>
       <c r="O12" s="43" t="n"/>
       <c r="P12" s="43" t="n"/>
-      <c r="Q12" s="41" t="n"/>
-      <c r="R12" s="44" t="n"/>
+      <c r="T12" s="41" t="n"/>
+      <c r="U12" s="44" t="n"/>
     </row>
     <row r="13" ht="22.05" customHeight="1">
       <c r="A13" s="33" t="n">
@@ -1907,8 +1972,8 @@
       <c r="N13" s="37" t="n"/>
       <c r="O13" s="37" t="n"/>
       <c r="P13" s="37" t="n"/>
-      <c r="Q13" s="35" t="n"/>
-      <c r="R13" s="38" t="n"/>
+      <c r="T13" s="35" t="n"/>
+      <c r="U13" s="38" t="n"/>
     </row>
     <row r="14" ht="22.05" customHeight="1">
       <c r="A14" s="39" t="n">
@@ -1961,8 +2026,8 @@
       <c r="N14" s="43" t="n"/>
       <c r="O14" s="43" t="n"/>
       <c r="P14" s="43" t="n"/>
-      <c r="Q14" s="41" t="n"/>
-      <c r="R14" s="44" t="n"/>
+      <c r="T14" s="41" t="n"/>
+      <c r="U14" s="44" t="n"/>
     </row>
     <row r="15" ht="22.05" customHeight="1">
       <c r="A15" s="33" t="n">
@@ -2015,8 +2080,8 @@
       <c r="N15" s="37" t="n"/>
       <c r="O15" s="37" t="n"/>
       <c r="P15" s="37" t="n"/>
-      <c r="Q15" s="35" t="n"/>
-      <c r="R15" s="38" t="n"/>
+      <c r="T15" s="35" t="n"/>
+      <c r="U15" s="38" t="n"/>
     </row>
     <row r="16" ht="22.05" customHeight="1">
       <c r="A16" s="39" t="n">
@@ -2075,8 +2140,8 @@
       <c r="N16" s="43" t="n"/>
       <c r="O16" s="43" t="n"/>
       <c r="P16" s="43" t="n"/>
-      <c r="Q16" s="41" t="n"/>
-      <c r="R16" s="44" t="n"/>
+      <c r="T16" s="41" t="n"/>
+      <c r="U16" s="44" t="n"/>
     </row>
     <row r="17" ht="22.05" customHeight="1">
       <c r="A17" s="33" t="n">
@@ -2135,8 +2200,8 @@
       <c r="N17" s="37" t="n"/>
       <c r="O17" s="37" t="n"/>
       <c r="P17" s="37" t="n"/>
-      <c r="Q17" s="35" t="n"/>
-      <c r="R17" s="38" t="n"/>
+      <c r="T17" s="35" t="n"/>
+      <c r="U17" s="38" t="n"/>
     </row>
     <row r="18" ht="22.05" customHeight="1">
       <c r="A18" s="39" t="n">
@@ -2189,8 +2254,8 @@
       <c r="N18" s="43" t="n"/>
       <c r="O18" s="43" t="n"/>
       <c r="P18" s="43" t="n"/>
-      <c r="Q18" s="41" t="n"/>
-      <c r="R18" s="44" t="n"/>
+      <c r="T18" s="41" t="n"/>
+      <c r="U18" s="44" t="n"/>
     </row>
     <row r="19" ht="22.05" customHeight="1">
       <c r="A19" s="33" t="n">
@@ -2243,8 +2308,8 @@
       <c r="N19" s="37" t="n"/>
       <c r="O19" s="37" t="n"/>
       <c r="P19" s="37" t="n"/>
-      <c r="Q19" s="35" t="n"/>
-      <c r="R19" s="38" t="n"/>
+      <c r="T19" s="35" t="n"/>
+      <c r="U19" s="38" t="n"/>
     </row>
     <row r="20" ht="22.05" customHeight="1">
       <c r="A20" s="39" t="n">
@@ -2297,8 +2362,8 @@
       <c r="N20" s="43" t="n"/>
       <c r="O20" s="43" t="n"/>
       <c r="P20" s="43" t="n"/>
-      <c r="Q20" s="41" t="n"/>
-      <c r="R20" s="44" t="n"/>
+      <c r="T20" s="41" t="n"/>
+      <c r="U20" s="44" t="n"/>
     </row>
     <row r="21" ht="22.05" customHeight="1">
       <c r="A21" s="33" t="n">
@@ -2351,8 +2416,8 @@
       <c r="N21" s="37" t="n"/>
       <c r="O21" s="37" t="n"/>
       <c r="P21" s="37" t="n"/>
-      <c r="Q21" s="35" t="n"/>
-      <c r="R21" s="38" t="n"/>
+      <c r="T21" s="35" t="n"/>
+      <c r="U21" s="38" t="n"/>
     </row>
     <row r="22" ht="22.05" customHeight="1">
       <c r="A22" s="39" t="n">
@@ -2405,8 +2470,8 @@
       <c r="N22" s="43" t="n"/>
       <c r="O22" s="43" t="n"/>
       <c r="P22" s="43" t="n"/>
-      <c r="Q22" s="41" t="n"/>
-      <c r="R22" s="44" t="n"/>
+      <c r="T22" s="41" t="n"/>
+      <c r="U22" s="44" t="n"/>
     </row>
     <row r="23" ht="22.05" customHeight="1">
       <c r="A23" s="33" t="n">
@@ -2459,8 +2524,8 @@
       <c r="N23" s="37" t="n"/>
       <c r="O23" s="37" t="n"/>
       <c r="P23" s="37" t="n"/>
-      <c r="Q23" s="35" t="n"/>
-      <c r="R23" s="38" t="n"/>
+      <c r="T23" s="35" t="n"/>
+      <c r="U23" s="38" t="n"/>
     </row>
     <row r="24" ht="22.05" customHeight="1">
       <c r="A24" s="39" t="n">
@@ -2513,8 +2578,8 @@
       <c r="N24" s="43" t="n"/>
       <c r="O24" s="43" t="n"/>
       <c r="P24" s="43" t="n"/>
-      <c r="Q24" s="41" t="n"/>
-      <c r="R24" s="44" t="n"/>
+      <c r="T24" s="41" t="n"/>
+      <c r="U24" s="44" t="n"/>
     </row>
     <row r="25" ht="22.05" customHeight="1">
       <c r="A25" s="33" t="n">
@@ -2567,8 +2632,8 @@
       <c r="N25" s="37" t="n"/>
       <c r="O25" s="37" t="n"/>
       <c r="P25" s="37" t="n"/>
-      <c r="Q25" s="35" t="n"/>
-      <c r="R25" s="38" t="n"/>
+      <c r="T25" s="35" t="n"/>
+      <c r="U25" s="38" t="n"/>
     </row>
     <row r="26" ht="22.05" customHeight="1">
       <c r="A26" s="39" t="n">
@@ -2621,8 +2686,8 @@
       <c r="N26" s="43" t="n"/>
       <c r="O26" s="43" t="n"/>
       <c r="P26" s="43" t="n"/>
-      <c r="Q26" s="41" t="n"/>
-      <c r="R26" s="44" t="n"/>
+      <c r="T26" s="41" t="n"/>
+      <c r="U26" s="44" t="n"/>
     </row>
     <row r="27" ht="22.05" customHeight="1">
       <c r="A27" s="33" t="n">
@@ -2675,8 +2740,8 @@
       <c r="N27" s="37" t="n"/>
       <c r="O27" s="37" t="n"/>
       <c r="P27" s="37" t="n"/>
-      <c r="Q27" s="35" t="n"/>
-      <c r="R27" s="38" t="n"/>
+      <c r="T27" s="35" t="n"/>
+      <c r="U27" s="38" t="n"/>
     </row>
     <row r="28" ht="22.05" customHeight="1">
       <c r="A28" s="39" t="n"/>
@@ -2695,8 +2760,8 @@
       <c r="N28" s="41" t="n"/>
       <c r="O28" s="41" t="n"/>
       <c r="P28" s="41" t="n"/>
-      <c r="Q28" s="41" t="n"/>
-      <c r="R28" s="44" t="n"/>
+      <c r="T28" s="41" t="n"/>
+      <c r="U28" s="44" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="33" t="n"/>
@@ -2715,8 +2780,8 @@
       <c r="N29" s="35" t="n"/>
       <c r="O29" s="35" t="n"/>
       <c r="P29" s="35" t="n"/>
-      <c r="Q29" s="35" t="n"/>
-      <c r="R29" s="38" t="n"/>
+      <c r="T29" s="35" t="n"/>
+      <c r="U29" s="38" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="39" t="n"/>
@@ -2735,8 +2800,8 @@
       <c r="N30" s="41" t="n"/>
       <c r="O30" s="41" t="n"/>
       <c r="P30" s="41" t="n"/>
-      <c r="Q30" s="41" t="n"/>
-      <c r="R30" s="44" t="n"/>
+      <c r="T30" s="41" t="n"/>
+      <c r="U30" s="44" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="33" t="n"/>
@@ -2755,8 +2820,8 @@
       <c r="N31" s="35" t="n"/>
       <c r="O31" s="35" t="n"/>
       <c r="P31" s="35" t="n"/>
-      <c r="Q31" s="35" t="n"/>
-      <c r="R31" s="38" t="n"/>
+      <c r="T31" s="35" t="n"/>
+      <c r="U31" s="38" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="39" t="n"/>
@@ -2775,8 +2840,8 @@
       <c r="N32" s="41" t="n"/>
       <c r="O32" s="41" t="n"/>
       <c r="P32" s="41" t="n"/>
-      <c r="Q32" s="41" t="n"/>
-      <c r="R32" s="44" t="n"/>
+      <c r="T32" s="41" t="n"/>
+      <c r="U32" s="44" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="33" t="n"/>
@@ -2795,8 +2860,8 @@
       <c r="N33" s="35" t="n"/>
       <c r="O33" s="35" t="n"/>
       <c r="P33" s="35" t="n"/>
-      <c r="Q33" s="35" t="n"/>
-      <c r="R33" s="38" t="n"/>
+      <c r="T33" s="35" t="n"/>
+      <c r="U33" s="38" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="39" t="n"/>
@@ -2815,8 +2880,8 @@
       <c r="N34" s="41" t="n"/>
       <c r="O34" s="41" t="n"/>
       <c r="P34" s="41" t="n"/>
-      <c r="Q34" s="41" t="n"/>
-      <c r="R34" s="44" t="n"/>
+      <c r="T34" s="41" t="n"/>
+      <c r="U34" s="44" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="33" t="n"/>
@@ -2835,8 +2900,8 @@
       <c r="N35" s="35" t="n"/>
       <c r="O35" s="35" t="n"/>
       <c r="P35" s="35" t="n"/>
-      <c r="Q35" s="35" t="n"/>
-      <c r="R35" s="38" t="n"/>
+      <c r="T35" s="35" t="n"/>
+      <c r="U35" s="38" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="39" t="n"/>
@@ -2855,8 +2920,8 @@
       <c r="N36" s="41" t="n"/>
       <c r="O36" s="41" t="n"/>
       <c r="P36" s="41" t="n"/>
-      <c r="Q36" s="41" t="n"/>
-      <c r="R36" s="44" t="n"/>
+      <c r="T36" s="41" t="n"/>
+      <c r="U36" s="44" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="33" t="n"/>
@@ -2875,8 +2940,8 @@
       <c r="N37" s="35" t="n"/>
       <c r="O37" s="35" t="n"/>
       <c r="P37" s="35" t="n"/>
-      <c r="Q37" s="35" t="n"/>
-      <c r="R37" s="38" t="n"/>
+      <c r="T37" s="35" t="n"/>
+      <c r="U37" s="38" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="39" t="n"/>
@@ -2895,8 +2960,8 @@
       <c r="N38" s="41" t="n"/>
       <c r="O38" s="41" t="n"/>
       <c r="P38" s="41" t="n"/>
-      <c r="Q38" s="41" t="n"/>
-      <c r="R38" s="44" t="n"/>
+      <c r="T38" s="41" t="n"/>
+      <c r="U38" s="44" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="33" t="n"/>
@@ -2915,8 +2980,8 @@
       <c r="N39" s="35" t="n"/>
       <c r="O39" s="35" t="n"/>
       <c r="P39" s="35" t="n"/>
-      <c r="Q39" s="35" t="n"/>
-      <c r="R39" s="38" t="n"/>
+      <c r="T39" s="35" t="n"/>
+      <c r="U39" s="38" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="39" t="n"/>
@@ -2935,8 +3000,8 @@
       <c r="N40" s="41" t="n"/>
       <c r="O40" s="41" t="n"/>
       <c r="P40" s="41" t="n"/>
-      <c r="Q40" s="41" t="n"/>
-      <c r="R40" s="44" t="n"/>
+      <c r="T40" s="41" t="n"/>
+      <c r="U40" s="44" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="33" t="n"/>
@@ -2955,8 +3020,8 @@
       <c r="N41" s="35" t="n"/>
       <c r="O41" s="35" t="n"/>
       <c r="P41" s="35" t="n"/>
-      <c r="Q41" s="35" t="n"/>
-      <c r="R41" s="38" t="n"/>
+      <c r="T41" s="35" t="n"/>
+      <c r="U41" s="38" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="39" t="n"/>
@@ -2975,8 +3040,8 @@
       <c r="N42" s="41" t="n"/>
       <c r="O42" s="41" t="n"/>
       <c r="P42" s="41" t="n"/>
-      <c r="Q42" s="41" t="n"/>
-      <c r="R42" s="44" t="n"/>
+      <c r="T42" s="41" t="n"/>
+      <c r="U42" s="44" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="33" t="n"/>
@@ -2995,8 +3060,8 @@
       <c r="N43" s="35" t="n"/>
       <c r="O43" s="35" t="n"/>
       <c r="P43" s="35" t="n"/>
-      <c r="Q43" s="35" t="n"/>
-      <c r="R43" s="38" t="n"/>
+      <c r="T43" s="35" t="n"/>
+      <c r="U43" s="38" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="39" t="n"/>
@@ -3015,8 +3080,8 @@
       <c r="N44" s="41" t="n"/>
       <c r="O44" s="41" t="n"/>
       <c r="P44" s="41" t="n"/>
-      <c r="Q44" s="41" t="n"/>
-      <c r="R44" s="44" t="n"/>
+      <c r="T44" s="41" t="n"/>
+      <c r="U44" s="44" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="33" t="n"/>
@@ -3035,8 +3100,8 @@
       <c r="N45" s="35" t="n"/>
       <c r="O45" s="35" t="n"/>
       <c r="P45" s="35" t="n"/>
-      <c r="Q45" s="35" t="n"/>
-      <c r="R45" s="38" t="n"/>
+      <c r="T45" s="35" t="n"/>
+      <c r="U45" s="38" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="39" t="n"/>
@@ -3055,8 +3120,8 @@
       <c r="N46" s="41" t="n"/>
       <c r="O46" s="41" t="n"/>
       <c r="P46" s="41" t="n"/>
-      <c r="Q46" s="41" t="n"/>
-      <c r="R46" s="44" t="n"/>
+      <c r="T46" s="41" t="n"/>
+      <c r="U46" s="44" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="33" t="n"/>
@@ -3075,8 +3140,8 @@
       <c r="N47" s="35" t="n"/>
       <c r="O47" s="35" t="n"/>
       <c r="P47" s="35" t="n"/>
-      <c r="Q47" s="35" t="n"/>
-      <c r="R47" s="38" t="n"/>
+      <c r="T47" s="35" t="n"/>
+      <c r="U47" s="38" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="39" t="n"/>
@@ -3095,8 +3160,8 @@
       <c r="N48" s="41" t="n"/>
       <c r="O48" s="41" t="n"/>
       <c r="P48" s="41" t="n"/>
-      <c r="Q48" s="41" t="n"/>
-      <c r="R48" s="44" t="n"/>
+      <c r="T48" s="41" t="n"/>
+      <c r="U48" s="44" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="33" t="n"/>
@@ -3115,8 +3180,8 @@
       <c r="N49" s="35" t="n"/>
       <c r="O49" s="35" t="n"/>
       <c r="P49" s="35" t="n"/>
-      <c r="Q49" s="35" t="n"/>
-      <c r="R49" s="38" t="n"/>
+      <c r="T49" s="35" t="n"/>
+      <c r="U49" s="38" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="39" t="n"/>
@@ -3135,8 +3200,8 @@
       <c r="N50" s="41" t="n"/>
       <c r="O50" s="41" t="n"/>
       <c r="P50" s="41" t="n"/>
-      <c r="Q50" s="41" t="n"/>
-      <c r="R50" s="44" t="n"/>
+      <c r="T50" s="41" t="n"/>
+      <c r="U50" s="44" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="33" t="n"/>
@@ -3155,8 +3220,8 @@
       <c r="N51" s="35" t="n"/>
       <c r="O51" s="35" t="n"/>
       <c r="P51" s="35" t="n"/>
-      <c r="Q51" s="35" t="n"/>
-      <c r="R51" s="38" t="n"/>
+      <c r="T51" s="35" t="n"/>
+      <c r="U51" s="38" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="39" t="n"/>
@@ -3175,8 +3240,8 @@
       <c r="N52" s="41" t="n"/>
       <c r="O52" s="41" t="n"/>
       <c r="P52" s="41" t="n"/>
-      <c r="Q52" s="41" t="n"/>
-      <c r="R52" s="44" t="n"/>
+      <c r="T52" s="41" t="n"/>
+      <c r="U52" s="44" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="33" t="n"/>
@@ -3195,8 +3260,8 @@
       <c r="N53" s="35" t="n"/>
       <c r="O53" s="35" t="n"/>
       <c r="P53" s="35" t="n"/>
-      <c r="Q53" s="35" t="n"/>
-      <c r="R53" s="38" t="n"/>
+      <c r="T53" s="35" t="n"/>
+      <c r="U53" s="38" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="39" t="n"/>
@@ -3215,8 +3280,8 @@
       <c r="N54" s="41" t="n"/>
       <c r="O54" s="41" t="n"/>
       <c r="P54" s="41" t="n"/>
-      <c r="Q54" s="41" t="n"/>
-      <c r="R54" s="44" t="n"/>
+      <c r="T54" s="41" t="n"/>
+      <c r="U54" s="44" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="33" t="n"/>
@@ -3235,8 +3300,8 @@
       <c r="N55" s="35" t="n"/>
       <c r="O55" s="35" t="n"/>
       <c r="P55" s="35" t="n"/>
-      <c r="Q55" s="35" t="n"/>
-      <c r="R55" s="38" t="n"/>
+      <c r="T55" s="35" t="n"/>
+      <c r="U55" s="38" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="39" t="n"/>
@@ -3255,8 +3320,8 @@
       <c r="N56" s="41" t="n"/>
       <c r="O56" s="41" t="n"/>
       <c r="P56" s="41" t="n"/>
-      <c r="Q56" s="41" t="n"/>
-      <c r="R56" s="44" t="n"/>
+      <c r="T56" s="41" t="n"/>
+      <c r="U56" s="44" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="33" t="n"/>
@@ -3275,8 +3340,8 @@
       <c r="N57" s="35" t="n"/>
       <c r="O57" s="35" t="n"/>
       <c r="P57" s="35" t="n"/>
-      <c r="Q57" s="35" t="n"/>
-      <c r="R57" s="38" t="n"/>
+      <c r="T57" s="35" t="n"/>
+      <c r="U57" s="38" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
@@ -364,7 +364,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -605,6 +605,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="20" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -837,6 +849,27 @@
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
         <t>▣ 메뉴얼
+(직접 입력)</t>
+      </text>
+    </comment>
+    <comment ref="Q4" authorId="0" shapeId="0">
+      <text>
+        <t>▣ 제안서
+완료일
+(직접 입력)</t>
+      </text>
+    </comment>
+    <comment ref="R4" authorId="0" shapeId="0">
+      <text>
+        <t>▣ 설계
+완료일
+(직접 입력)</t>
+      </text>
+    </comment>
+    <comment ref="S4" authorId="0" shapeId="0">
+      <text>
+        <t>▣ 가공의뢰
+입고일
 (직접 입력)</t>
       </text>
     </comment>
@@ -1167,11 +1200,13 @@
     <col width="8" customWidth="1" style="68" min="16" max="16"/>
     <col width="12" customWidth="1" style="68" min="17" max="17"/>
     <col width="12" customWidth="1" style="68" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" style="68" min="19" max="19"/>
+    <col width="10" customWidth="1" style="68" min="20" max="20"/>
+    <col width="28" customWidth="1" style="68" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="75" t="inlineStr">
+      <c r="A1" s="80" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 설계팀 │ 2026</t>
         </is>
@@ -1191,11 +1226,14 @@
       <c r="N1" s="46" t="n"/>
       <c r="O1" s="46" t="n"/>
       <c r="P1" s="46" t="n"/>
+      <c r="Q1" s="46" t="n"/>
+      <c r="R1" s="46" t="n"/>
+      <c r="S1" s="46" t="n"/>
       <c r="T1" s="46" t="n"/>
       <c r="U1" s="47" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="76" t="inlineStr">
+      <c r="A2" s="81" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 설계팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1215,10 +1253,13 @@
       <c r="N2" s="46" t="n"/>
       <c r="O2" s="46" t="n"/>
       <c r="P2" s="46" t="n"/>
+      <c r="Q2" s="46" t="n"/>
+      <c r="R2" s="46" t="n"/>
+      <c r="S2" s="46" t="n"/>
       <c r="T2" s="47" t="n"/>
-      <c r="U2" s="77" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 01:42</t>
+      <c r="U2" s="82" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 00:45</t>
         </is>
       </c>
     </row>
@@ -1303,19 +1344,19 @@
           <t>✏입력</t>
         </is>
       </c>
-      <c r="Q3" s="78" t="inlineStr">
-        <is>
-          <t>✏입력</t>
-        </is>
-      </c>
-      <c r="R3" s="78" t="inlineStr">
-        <is>
-          <t>✏입력</t>
-        </is>
-      </c>
-      <c r="S3" s="78" t="inlineStr">
-        <is>
-          <t>✏입력</t>
+      <c r="Q3" s="29" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="R3" s="29" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="S3" s="29" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
         </is>
       </c>
       <c r="T3" s="28" t="inlineStr">
@@ -1410,19 +1451,19 @@
           <t>메뉴얼</t>
         </is>
       </c>
-      <c r="Q4" s="79" t="inlineStr">
+      <c r="Q4" s="83" t="inlineStr">
         <is>
           <t>제안서
 완료일</t>
         </is>
       </c>
-      <c r="R4" s="79" t="inlineStr">
+      <c r="R4" s="83" t="inlineStr">
         <is>
           <t>설계
 완료일</t>
         </is>
       </c>
-      <c r="S4" s="79" t="inlineStr">
+      <c r="S4" s="83" t="inlineStr">
         <is>
           <t>가공의뢰
 입고일</t>
@@ -1506,6 +1547,9 @@
       <c r="P5" s="37" t="n">
         <v>0.5</v>
       </c>
+      <c r="Q5" s="35" t="n"/>
+      <c r="R5" s="35" t="n"/>
+      <c r="S5" s="35" t="n"/>
       <c r="T5" s="35" t="inlineStr">
         <is>
           <t>진행중</t>
@@ -1576,6 +1620,9 @@
       <c r="P6" s="43" t="n">
         <v>0.1</v>
       </c>
+      <c r="Q6" s="41" t="n"/>
+      <c r="R6" s="41" t="n"/>
+      <c r="S6" s="41" t="n"/>
       <c r="T6" s="41" t="inlineStr">
         <is>
           <t>진행중</t>
@@ -1644,6 +1691,9 @@
       <c r="P7" s="37" t="n">
         <v>0</v>
       </c>
+      <c r="Q7" s="35" t="n"/>
+      <c r="R7" s="35" t="n"/>
+      <c r="S7" s="35" t="n"/>
       <c r="T7" s="35" t="inlineStr">
         <is>
           <t>진행중</t>
@@ -1702,6 +1752,9 @@
       <c r="N8" s="43" t="n"/>
       <c r="O8" s="43" t="n"/>
       <c r="P8" s="43" t="n"/>
+      <c r="Q8" s="41" t="n"/>
+      <c r="R8" s="41" t="n"/>
+      <c r="S8" s="41" t="n"/>
       <c r="T8" s="41" t="n"/>
       <c r="U8" s="44" t="n"/>
     </row>
@@ -1756,6 +1809,9 @@
       <c r="N9" s="37" t="n"/>
       <c r="O9" s="37" t="n"/>
       <c r="P9" s="37" t="n"/>
+      <c r="Q9" s="35" t="n"/>
+      <c r="R9" s="35" t="n"/>
+      <c r="S9" s="35" t="n"/>
       <c r="T9" s="35" t="n"/>
       <c r="U9" s="38" t="n"/>
     </row>
@@ -1810,6 +1866,9 @@
       <c r="N10" s="43" t="n"/>
       <c r="O10" s="43" t="n"/>
       <c r="P10" s="43" t="n"/>
+      <c r="Q10" s="41" t="n"/>
+      <c r="R10" s="41" t="n"/>
+      <c r="S10" s="41" t="n"/>
       <c r="T10" s="41" t="n"/>
       <c r="U10" s="44" t="n"/>
     </row>
@@ -1864,6 +1923,9 @@
       <c r="N11" s="37" t="n"/>
       <c r="O11" s="37" t="n"/>
       <c r="P11" s="37" t="n"/>
+      <c r="Q11" s="35" t="n"/>
+      <c r="R11" s="35" t="n"/>
+      <c r="S11" s="35" t="n"/>
       <c r="T11" s="35" t="n"/>
       <c r="U11" s="38" t="n"/>
     </row>
@@ -1918,6 +1980,9 @@
       <c r="N12" s="43" t="n"/>
       <c r="O12" s="43" t="n"/>
       <c r="P12" s="43" t="n"/>
+      <c r="Q12" s="41" t="n"/>
+      <c r="R12" s="41" t="n"/>
+      <c r="S12" s="41" t="n"/>
       <c r="T12" s="41" t="n"/>
       <c r="U12" s="44" t="n"/>
     </row>
@@ -1972,6 +2037,9 @@
       <c r="N13" s="37" t="n"/>
       <c r="O13" s="37" t="n"/>
       <c r="P13" s="37" t="n"/>
+      <c r="Q13" s="35" t="n"/>
+      <c r="R13" s="35" t="n"/>
+      <c r="S13" s="35" t="n"/>
       <c r="T13" s="35" t="n"/>
       <c r="U13" s="38" t="n"/>
     </row>
@@ -2026,6 +2094,9 @@
       <c r="N14" s="43" t="n"/>
       <c r="O14" s="43" t="n"/>
       <c r="P14" s="43" t="n"/>
+      <c r="Q14" s="41" t="n"/>
+      <c r="R14" s="41" t="n"/>
+      <c r="S14" s="41" t="n"/>
       <c r="T14" s="41" t="n"/>
       <c r="U14" s="44" t="n"/>
     </row>
@@ -2080,6 +2151,9 @@
       <c r="N15" s="37" t="n"/>
       <c r="O15" s="37" t="n"/>
       <c r="P15" s="37" t="n"/>
+      <c r="Q15" s="35" t="n"/>
+      <c r="R15" s="35" t="n"/>
+      <c r="S15" s="35" t="n"/>
       <c r="T15" s="35" t="n"/>
       <c r="U15" s="38" t="n"/>
     </row>
@@ -2140,6 +2214,9 @@
       <c r="N16" s="43" t="n"/>
       <c r="O16" s="43" t="n"/>
       <c r="P16" s="43" t="n"/>
+      <c r="Q16" s="41" t="n"/>
+      <c r="R16" s="41" t="n"/>
+      <c r="S16" s="41" t="n"/>
       <c r="T16" s="41" t="n"/>
       <c r="U16" s="44" t="n"/>
     </row>
@@ -2200,6 +2277,9 @@
       <c r="N17" s="37" t="n"/>
       <c r="O17" s="37" t="n"/>
       <c r="P17" s="37" t="n"/>
+      <c r="Q17" s="35" t="n"/>
+      <c r="R17" s="35" t="n"/>
+      <c r="S17" s="35" t="n"/>
       <c r="T17" s="35" t="n"/>
       <c r="U17" s="38" t="n"/>
     </row>
@@ -2254,6 +2334,9 @@
       <c r="N18" s="43" t="n"/>
       <c r="O18" s="43" t="n"/>
       <c r="P18" s="43" t="n"/>
+      <c r="Q18" s="41" t="n"/>
+      <c r="R18" s="41" t="n"/>
+      <c r="S18" s="41" t="n"/>
       <c r="T18" s="41" t="n"/>
       <c r="U18" s="44" t="n"/>
     </row>
@@ -2308,6 +2391,9 @@
       <c r="N19" s="37" t="n"/>
       <c r="O19" s="37" t="n"/>
       <c r="P19" s="37" t="n"/>
+      <c r="Q19" s="35" t="n"/>
+      <c r="R19" s="35" t="n"/>
+      <c r="S19" s="35" t="n"/>
       <c r="T19" s="35" t="n"/>
       <c r="U19" s="38" t="n"/>
     </row>
@@ -2362,6 +2448,9 @@
       <c r="N20" s="43" t="n"/>
       <c r="O20" s="43" t="n"/>
       <c r="P20" s="43" t="n"/>
+      <c r="Q20" s="41" t="n"/>
+      <c r="R20" s="41" t="n"/>
+      <c r="S20" s="41" t="n"/>
       <c r="T20" s="41" t="n"/>
       <c r="U20" s="44" t="n"/>
     </row>
@@ -2416,6 +2505,9 @@
       <c r="N21" s="37" t="n"/>
       <c r="O21" s="37" t="n"/>
       <c r="P21" s="37" t="n"/>
+      <c r="Q21" s="35" t="n"/>
+      <c r="R21" s="35" t="n"/>
+      <c r="S21" s="35" t="n"/>
       <c r="T21" s="35" t="n"/>
       <c r="U21" s="38" t="n"/>
     </row>
@@ -2470,6 +2562,9 @@
       <c r="N22" s="43" t="n"/>
       <c r="O22" s="43" t="n"/>
       <c r="P22" s="43" t="n"/>
+      <c r="Q22" s="41" t="n"/>
+      <c r="R22" s="41" t="n"/>
+      <c r="S22" s="41" t="n"/>
       <c r="T22" s="41" t="n"/>
       <c r="U22" s="44" t="n"/>
     </row>
@@ -2524,6 +2619,9 @@
       <c r="N23" s="37" t="n"/>
       <c r="O23" s="37" t="n"/>
       <c r="P23" s="37" t="n"/>
+      <c r="Q23" s="35" t="n"/>
+      <c r="R23" s="35" t="n"/>
+      <c r="S23" s="35" t="n"/>
       <c r="T23" s="35" t="n"/>
       <c r="U23" s="38" t="n"/>
     </row>
@@ -2578,6 +2676,9 @@
       <c r="N24" s="43" t="n"/>
       <c r="O24" s="43" t="n"/>
       <c r="P24" s="43" t="n"/>
+      <c r="Q24" s="41" t="n"/>
+      <c r="R24" s="41" t="n"/>
+      <c r="S24" s="41" t="n"/>
       <c r="T24" s="41" t="n"/>
       <c r="U24" s="44" t="n"/>
     </row>
@@ -2632,6 +2733,9 @@
       <c r="N25" s="37" t="n"/>
       <c r="O25" s="37" t="n"/>
       <c r="P25" s="37" t="n"/>
+      <c r="Q25" s="35" t="n"/>
+      <c r="R25" s="35" t="n"/>
+      <c r="S25" s="35" t="n"/>
       <c r="T25" s="35" t="n"/>
       <c r="U25" s="38" t="n"/>
     </row>
@@ -2686,6 +2790,9 @@
       <c r="N26" s="43" t="n"/>
       <c r="O26" s="43" t="n"/>
       <c r="P26" s="43" t="n"/>
+      <c r="Q26" s="41" t="n"/>
+      <c r="R26" s="41" t="n"/>
+      <c r="S26" s="41" t="n"/>
       <c r="T26" s="41" t="n"/>
       <c r="U26" s="44" t="n"/>
     </row>
@@ -2740,6 +2847,9 @@
       <c r="N27" s="37" t="n"/>
       <c r="O27" s="37" t="n"/>
       <c r="P27" s="37" t="n"/>
+      <c r="Q27" s="35" t="n"/>
+      <c r="R27" s="35" t="n"/>
+      <c r="S27" s="35" t="n"/>
       <c r="T27" s="35" t="n"/>
       <c r="U27" s="38" t="n"/>
     </row>
@@ -2760,6 +2870,9 @@
       <c r="N28" s="41" t="n"/>
       <c r="O28" s="41" t="n"/>
       <c r="P28" s="41" t="n"/>
+      <c r="Q28" s="41" t="n"/>
+      <c r="R28" s="41" t="n"/>
+      <c r="S28" s="41" t="n"/>
       <c r="T28" s="41" t="n"/>
       <c r="U28" s="44" t="n"/>
     </row>
@@ -2780,6 +2893,9 @@
       <c r="N29" s="35" t="n"/>
       <c r="O29" s="35" t="n"/>
       <c r="P29" s="35" t="n"/>
+      <c r="Q29" s="35" t="n"/>
+      <c r="R29" s="35" t="n"/>
+      <c r="S29" s="35" t="n"/>
       <c r="T29" s="35" t="n"/>
       <c r="U29" s="38" t="n"/>
     </row>
@@ -2800,6 +2916,9 @@
       <c r="N30" s="41" t="n"/>
       <c r="O30" s="41" t="n"/>
       <c r="P30" s="41" t="n"/>
+      <c r="Q30" s="41" t="n"/>
+      <c r="R30" s="41" t="n"/>
+      <c r="S30" s="41" t="n"/>
       <c r="T30" s="41" t="n"/>
       <c r="U30" s="44" t="n"/>
     </row>
@@ -2820,6 +2939,9 @@
       <c r="N31" s="35" t="n"/>
       <c r="O31" s="35" t="n"/>
       <c r="P31" s="35" t="n"/>
+      <c r="Q31" s="35" t="n"/>
+      <c r="R31" s="35" t="n"/>
+      <c r="S31" s="35" t="n"/>
       <c r="T31" s="35" t="n"/>
       <c r="U31" s="38" t="n"/>
     </row>
@@ -2840,6 +2962,9 @@
       <c r="N32" s="41" t="n"/>
       <c r="O32" s="41" t="n"/>
       <c r="P32" s="41" t="n"/>
+      <c r="Q32" s="41" t="n"/>
+      <c r="R32" s="41" t="n"/>
+      <c r="S32" s="41" t="n"/>
       <c r="T32" s="41" t="n"/>
       <c r="U32" s="44" t="n"/>
     </row>
@@ -2860,6 +2985,9 @@
       <c r="N33" s="35" t="n"/>
       <c r="O33" s="35" t="n"/>
       <c r="P33" s="35" t="n"/>
+      <c r="Q33" s="35" t="n"/>
+      <c r="R33" s="35" t="n"/>
+      <c r="S33" s="35" t="n"/>
       <c r="T33" s="35" t="n"/>
       <c r="U33" s="38" t="n"/>
     </row>
@@ -2880,6 +3008,9 @@
       <c r="N34" s="41" t="n"/>
       <c r="O34" s="41" t="n"/>
       <c r="P34" s="41" t="n"/>
+      <c r="Q34" s="41" t="n"/>
+      <c r="R34" s="41" t="n"/>
+      <c r="S34" s="41" t="n"/>
       <c r="T34" s="41" t="n"/>
       <c r="U34" s="44" t="n"/>
     </row>
@@ -2900,6 +3031,9 @@
       <c r="N35" s="35" t="n"/>
       <c r="O35" s="35" t="n"/>
       <c r="P35" s="35" t="n"/>
+      <c r="Q35" s="35" t="n"/>
+      <c r="R35" s="35" t="n"/>
+      <c r="S35" s="35" t="n"/>
       <c r="T35" s="35" t="n"/>
       <c r="U35" s="38" t="n"/>
     </row>
@@ -2920,6 +3054,9 @@
       <c r="N36" s="41" t="n"/>
       <c r="O36" s="41" t="n"/>
       <c r="P36" s="41" t="n"/>
+      <c r="Q36" s="41" t="n"/>
+      <c r="R36" s="41" t="n"/>
+      <c r="S36" s="41" t="n"/>
       <c r="T36" s="41" t="n"/>
       <c r="U36" s="44" t="n"/>
     </row>
@@ -2940,6 +3077,9 @@
       <c r="N37" s="35" t="n"/>
       <c r="O37" s="35" t="n"/>
       <c r="P37" s="35" t="n"/>
+      <c r="Q37" s="35" t="n"/>
+      <c r="R37" s="35" t="n"/>
+      <c r="S37" s="35" t="n"/>
       <c r="T37" s="35" t="n"/>
       <c r="U37" s="38" t="n"/>
     </row>
@@ -2960,6 +3100,9 @@
       <c r="N38" s="41" t="n"/>
       <c r="O38" s="41" t="n"/>
       <c r="P38" s="41" t="n"/>
+      <c r="Q38" s="41" t="n"/>
+      <c r="R38" s="41" t="n"/>
+      <c r="S38" s="41" t="n"/>
       <c r="T38" s="41" t="n"/>
       <c r="U38" s="44" t="n"/>
     </row>
@@ -2980,6 +3123,9 @@
       <c r="N39" s="35" t="n"/>
       <c r="O39" s="35" t="n"/>
       <c r="P39" s="35" t="n"/>
+      <c r="Q39" s="35" t="n"/>
+      <c r="R39" s="35" t="n"/>
+      <c r="S39" s="35" t="n"/>
       <c r="T39" s="35" t="n"/>
       <c r="U39" s="38" t="n"/>
     </row>
@@ -3000,6 +3146,9 @@
       <c r="N40" s="41" t="n"/>
       <c r="O40" s="41" t="n"/>
       <c r="P40" s="41" t="n"/>
+      <c r="Q40" s="41" t="n"/>
+      <c r="R40" s="41" t="n"/>
+      <c r="S40" s="41" t="n"/>
       <c r="T40" s="41" t="n"/>
       <c r="U40" s="44" t="n"/>
     </row>
@@ -3020,6 +3169,9 @@
       <c r="N41" s="35" t="n"/>
       <c r="O41" s="35" t="n"/>
       <c r="P41" s="35" t="n"/>
+      <c r="Q41" s="35" t="n"/>
+      <c r="R41" s="35" t="n"/>
+      <c r="S41" s="35" t="n"/>
       <c r="T41" s="35" t="n"/>
       <c r="U41" s="38" t="n"/>
     </row>
@@ -3040,6 +3192,9 @@
       <c r="N42" s="41" t="n"/>
       <c r="O42" s="41" t="n"/>
       <c r="P42" s="41" t="n"/>
+      <c r="Q42" s="41" t="n"/>
+      <c r="R42" s="41" t="n"/>
+      <c r="S42" s="41" t="n"/>
       <c r="T42" s="41" t="n"/>
       <c r="U42" s="44" t="n"/>
     </row>
@@ -3060,6 +3215,9 @@
       <c r="N43" s="35" t="n"/>
       <c r="O43" s="35" t="n"/>
       <c r="P43" s="35" t="n"/>
+      <c r="Q43" s="35" t="n"/>
+      <c r="R43" s="35" t="n"/>
+      <c r="S43" s="35" t="n"/>
       <c r="T43" s="35" t="n"/>
       <c r="U43" s="38" t="n"/>
     </row>
@@ -3080,6 +3238,9 @@
       <c r="N44" s="41" t="n"/>
       <c r="O44" s="41" t="n"/>
       <c r="P44" s="41" t="n"/>
+      <c r="Q44" s="41" t="n"/>
+      <c r="R44" s="41" t="n"/>
+      <c r="S44" s="41" t="n"/>
       <c r="T44" s="41" t="n"/>
       <c r="U44" s="44" t="n"/>
     </row>
@@ -3100,6 +3261,9 @@
       <c r="N45" s="35" t="n"/>
       <c r="O45" s="35" t="n"/>
       <c r="P45" s="35" t="n"/>
+      <c r="Q45" s="35" t="n"/>
+      <c r="R45" s="35" t="n"/>
+      <c r="S45" s="35" t="n"/>
       <c r="T45" s="35" t="n"/>
       <c r="U45" s="38" t="n"/>
     </row>
@@ -3120,6 +3284,9 @@
       <c r="N46" s="41" t="n"/>
       <c r="O46" s="41" t="n"/>
       <c r="P46" s="41" t="n"/>
+      <c r="Q46" s="41" t="n"/>
+      <c r="R46" s="41" t="n"/>
+      <c r="S46" s="41" t="n"/>
       <c r="T46" s="41" t="n"/>
       <c r="U46" s="44" t="n"/>
     </row>
@@ -3140,6 +3307,9 @@
       <c r="N47" s="35" t="n"/>
       <c r="O47" s="35" t="n"/>
       <c r="P47" s="35" t="n"/>
+      <c r="Q47" s="35" t="n"/>
+      <c r="R47" s="35" t="n"/>
+      <c r="S47" s="35" t="n"/>
       <c r="T47" s="35" t="n"/>
       <c r="U47" s="38" t="n"/>
     </row>
@@ -3160,6 +3330,9 @@
       <c r="N48" s="41" t="n"/>
       <c r="O48" s="41" t="n"/>
       <c r="P48" s="41" t="n"/>
+      <c r="Q48" s="41" t="n"/>
+      <c r="R48" s="41" t="n"/>
+      <c r="S48" s="41" t="n"/>
       <c r="T48" s="41" t="n"/>
       <c r="U48" s="44" t="n"/>
     </row>
@@ -3180,6 +3353,9 @@
       <c r="N49" s="35" t="n"/>
       <c r="O49" s="35" t="n"/>
       <c r="P49" s="35" t="n"/>
+      <c r="Q49" s="35" t="n"/>
+      <c r="R49" s="35" t="n"/>
+      <c r="S49" s="35" t="n"/>
       <c r="T49" s="35" t="n"/>
       <c r="U49" s="38" t="n"/>
     </row>
@@ -3200,6 +3376,9 @@
       <c r="N50" s="41" t="n"/>
       <c r="O50" s="41" t="n"/>
       <c r="P50" s="41" t="n"/>
+      <c r="Q50" s="41" t="n"/>
+      <c r="R50" s="41" t="n"/>
+      <c r="S50" s="41" t="n"/>
       <c r="T50" s="41" t="n"/>
       <c r="U50" s="44" t="n"/>
     </row>
@@ -3220,6 +3399,9 @@
       <c r="N51" s="35" t="n"/>
       <c r="O51" s="35" t="n"/>
       <c r="P51" s="35" t="n"/>
+      <c r="Q51" s="35" t="n"/>
+      <c r="R51" s="35" t="n"/>
+      <c r="S51" s="35" t="n"/>
       <c r="T51" s="35" t="n"/>
       <c r="U51" s="38" t="n"/>
     </row>
@@ -3240,6 +3422,9 @@
       <c r="N52" s="41" t="n"/>
       <c r="O52" s="41" t="n"/>
       <c r="P52" s="41" t="n"/>
+      <c r="Q52" s="41" t="n"/>
+      <c r="R52" s="41" t="n"/>
+      <c r="S52" s="41" t="n"/>
       <c r="T52" s="41" t="n"/>
       <c r="U52" s="44" t="n"/>
     </row>
@@ -3260,6 +3445,9 @@
       <c r="N53" s="35" t="n"/>
       <c r="O53" s="35" t="n"/>
       <c r="P53" s="35" t="n"/>
+      <c r="Q53" s="35" t="n"/>
+      <c r="R53" s="35" t="n"/>
+      <c r="S53" s="35" t="n"/>
       <c r="T53" s="35" t="n"/>
       <c r="U53" s="38" t="n"/>
     </row>
@@ -3280,6 +3468,9 @@
       <c r="N54" s="41" t="n"/>
       <c r="O54" s="41" t="n"/>
       <c r="P54" s="41" t="n"/>
+      <c r="Q54" s="41" t="n"/>
+      <c r="R54" s="41" t="n"/>
+      <c r="S54" s="41" t="n"/>
       <c r="T54" s="41" t="n"/>
       <c r="U54" s="44" t="n"/>
     </row>
@@ -3300,6 +3491,9 @@
       <c r="N55" s="35" t="n"/>
       <c r="O55" s="35" t="n"/>
       <c r="P55" s="35" t="n"/>
+      <c r="Q55" s="35" t="n"/>
+      <c r="R55" s="35" t="n"/>
+      <c r="S55" s="35" t="n"/>
       <c r="T55" s="35" t="n"/>
       <c r="U55" s="38" t="n"/>
     </row>
@@ -3320,6 +3514,9 @@
       <c r="N56" s="41" t="n"/>
       <c r="O56" s="41" t="n"/>
       <c r="P56" s="41" t="n"/>
+      <c r="Q56" s="41" t="n"/>
+      <c r="R56" s="41" t="n"/>
+      <c r="S56" s="41" t="n"/>
       <c r="T56" s="41" t="n"/>
       <c r="U56" s="44" t="n"/>
     </row>
@@ -3340,14 +3537,17 @@
       <c r="N57" s="35" t="n"/>
       <c r="O57" s="35" t="n"/>
       <c r="P57" s="35" t="n"/>
+      <c r="Q57" s="35" t="n"/>
+      <c r="R57" s="35" t="n"/>
+      <c r="S57" s="35" t="n"/>
       <c r="T57" s="35" t="n"/>
       <c r="U57" s="38" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:T2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="Q5:Q28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
@@ -364,7 +364,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -618,6 +618,24 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="20" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -809,8 +827,11 @@
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 담당자
-(직접 입력)</t>
+        <t>▣ 부서 담당자
+• 부서 내 실제 담당자 이름 입력
+  예: 정민규, 한재운, 이찬
+• 입력 시: PMS에도 자동 반영
+• 빈 칸: 부서 참여 확정, 담당자 미정</t>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
@@ -824,65 +845,111 @@
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 상세컨셉
-(직접 입력)</t>
+        <t>▣ 상세컨셉 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 3D/2D설계
-(직접 입력)</t>
+        <t>▣ 3D/2D설계 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ BOM작성
-(직접 입력)</t>
+        <t>▣ BOM작성 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 가공품발주
-(직접 입력)</t>
+        <t>▣ 가공품발주 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메뉴얼
-(직접 입력)</t>
+        <t>▣ 메뉴얼 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 제안서
-완료일
-(직접 입력)</t>
+        <t>▣ 제안서 완료일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-05-15
+• 허용: 26-5-15, 260515, 2026.5.15 (자동 정규화)
+• 실제 제안서 작성·제출 완료된 날짜 기입
+• 비워두면 미완료 상태
+• 예정일이 아닌 ★실제 완료일★ 만 입력</t>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 설계
-완료일
-(직접 입력)</t>
+        <t>▣ 설계 완료일 (3D/2D 설계 완료)
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-06-30
+• 3D/2D 설계가 실제로 완료된 날짜
+• 비워두면 미완료
+• 예정일 아닌 실제 완료일</t>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 가공의뢰
-입고일
-(직접 입력)</t>
+        <t>▣ 가공의뢰 입고일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-10
+• 가공팀 의뢰분 또는 외주 가공품의
+  ★실제 입고된 날짜★ 기입 (내부·외주 무관)
+• 비워두면: 대시보드 외주현황에 '진행중' 표시
+• 입고일 입력 시: '입고완료'로 자동 분류</t>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 상태
-(직접 입력)</t>
+        <t>▣ 부서 작업 상태
+• 드롭다운 선택:
+  미착수 — 작업 시작 안 함
+  진행중 — 작업 진행 중
+  완료   — 부서 작업 완료
+  N/A    — 해당 부서 무관 프로젝트
+• 부서장이 매주 상태 갱신 권장</t>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메모
-(직접 입력)</t>
+        <t>▣ 메모 (부서 자유 입력)
+• 자유 텍스트 입력
+• 활용:
+  - 이슈사항 (예: 자재 결품, 외주 지연)
+  - 변경 요청 (예: 사양 변경, 납기 조정)
+  - 다른 부서·PM에게 공유할 정보
+• 대시보드 집계에는 미포함</t>
       </text>
     </comment>
   </commentList>
@@ -1206,7 +1273,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="80" t="inlineStr">
+      <c r="A1" s="87" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 설계팀 │ 2026</t>
         </is>
@@ -1233,7 +1300,7 @@
       <c r="U1" s="47" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="81" t="inlineStr">
+      <c r="A2" s="88" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 설계팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1257,9 +1324,9 @@
       <c r="R2" s="46" t="n"/>
       <c r="S2" s="46" t="n"/>
       <c r="T2" s="47" t="n"/>
-      <c r="U2" s="82" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 00:45</t>
+      <c r="U2" s="89" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:07</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
@@ -364,7 +364,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -618,6 +618,15 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="20" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1273,7 +1282,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="87" t="inlineStr">
+      <c r="A1" s="90" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 설계팀 │ 2026</t>
         </is>
@@ -1300,7 +1309,7 @@
       <c r="U1" s="47" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="88" t="inlineStr">
+      <c r="A2" s="91" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 설계팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1324,9 +1333,9 @@
       <c r="R2" s="46" t="n"/>
       <c r="S2" s="46" t="n"/>
       <c r="T2" s="47" t="n"/>
-      <c r="U2" s="89" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:07</t>
+      <c r="U2" s="92" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 02:01</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
@@ -364,7 +364,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -618,6 +618,15 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="20" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -845,11 +854,15 @@
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률(%)
-• 자동 계산 — 참여 부서 소계의 평균
-  예: 3개 부서 진척률 80/50/30 → 53%
-• sync 시 갱신, 수동 수정 불가
-• 100% = 전 부서 완료 상태</t>
+        <t>▣ 부서 진척률 (%) — 본인 부서 작업
+• 자동 계산 (수정 불가, sync 시 갱신)
+• 시작일·완료일 입력 기반:
+    0%  = 미착수    (시작일·완료일 모두 빈 칸)
+   50%  = 진행중    (시작일만 입력)
+  100%  = 완료      (완료일까지 입력)
+• ★ 이 값은 '이 부서'만의 진척률입니다.
+• 프로젝트 전체 진척률은 PMS 1_프로젝트등록
+  '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
@@ -1282,7 +1295,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="90" t="inlineStr">
+      <c r="A1" s="93" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 설계팀 │ 2026</t>
         </is>
@@ -1309,7 +1322,7 @@
       <c r="U1" s="47" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="91" t="inlineStr">
+      <c r="A2" s="94" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 설계팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1333,9 +1346,9 @@
       <c r="R2" s="46" t="n"/>
       <c r="S2" s="46" t="n"/>
       <c r="T2" s="47" t="n"/>
-      <c r="U2" s="92" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 02:01</t>
+      <c r="U2" s="95" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 11:54</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1512,7 @@
       </c>
       <c r="K4" s="30" t="inlineStr">
         <is>
-          <t>전체진척률(%)</t>
+          <t>부서진척률(%)</t>
         </is>
       </c>
       <c r="L4" s="32" t="inlineStr">

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="K5" s="36" t="n">
-        <v>0.009166666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="L5" s="37" t="n">
         <v>1</v>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="J6" s="41" t="n"/>
       <c r="K6" s="42" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="L6" s="43" t="n">
         <v>1</v>
@@ -1764,7 +1764,9 @@
         </is>
       </c>
       <c r="J7" s="35" t="n"/>
-      <c r="K7" s="36" t="inlineStr"/>
+      <c r="K7" s="36" t="n">
+        <v>0</v>
+      </c>
       <c r="L7" s="37" t="n">
         <v>1</v>
       </c>
@@ -1835,7 +1837,9 @@
         </is>
       </c>
       <c r="J8" s="41" t="n"/>
-      <c r="K8" s="42" t="inlineStr"/>
+      <c r="K8" s="42" t="n">
+        <v>0</v>
+      </c>
       <c r="L8" s="43" t="n"/>
       <c r="M8" s="43" t="n"/>
       <c r="N8" s="43" t="n"/>
@@ -1892,7 +1896,9 @@
         </is>
       </c>
       <c r="J9" s="35" t="n"/>
-      <c r="K9" s="36" t="inlineStr"/>
+      <c r="K9" s="36" t="n">
+        <v>0</v>
+      </c>
       <c r="L9" s="37" t="n"/>
       <c r="M9" s="37" t="n"/>
       <c r="N9" s="37" t="n"/>
@@ -1949,7 +1955,9 @@
         </is>
       </c>
       <c r="J10" s="41" t="n"/>
-      <c r="K10" s="42" t="inlineStr"/>
+      <c r="K10" s="42" t="n">
+        <v>0</v>
+      </c>
       <c r="L10" s="43" t="n"/>
       <c r="M10" s="43" t="n"/>
       <c r="N10" s="43" t="n"/>
@@ -2006,7 +2014,9 @@
         </is>
       </c>
       <c r="J11" s="35" t="n"/>
-      <c r="K11" s="36" t="inlineStr"/>
+      <c r="K11" s="36" t="n">
+        <v>0</v>
+      </c>
       <c r="L11" s="37" t="n"/>
       <c r="M11" s="37" t="n"/>
       <c r="N11" s="37" t="n"/>
@@ -2063,7 +2073,9 @@
         </is>
       </c>
       <c r="J12" s="41" t="n"/>
-      <c r="K12" s="42" t="inlineStr"/>
+      <c r="K12" s="42" t="n">
+        <v>0</v>
+      </c>
       <c r="L12" s="43" t="n"/>
       <c r="M12" s="43" t="n"/>
       <c r="N12" s="43" t="n"/>
@@ -2120,7 +2132,9 @@
         </is>
       </c>
       <c r="J13" s="35" t="n"/>
-      <c r="K13" s="36" t="inlineStr"/>
+      <c r="K13" s="36" t="n">
+        <v>0</v>
+      </c>
       <c r="L13" s="37" t="n"/>
       <c r="M13" s="37" t="n"/>
       <c r="N13" s="37" t="n"/>
@@ -2177,7 +2191,9 @@
         </is>
       </c>
       <c r="J14" s="41" t="n"/>
-      <c r="K14" s="42" t="inlineStr"/>
+      <c r="K14" s="42" t="n">
+        <v>0</v>
+      </c>
       <c r="L14" s="43" t="n"/>
       <c r="M14" s="43" t="n"/>
       <c r="N14" s="43" t="n"/>
@@ -2234,7 +2250,9 @@
         </is>
       </c>
       <c r="J15" s="35" t="n"/>
-      <c r="K15" s="36" t="inlineStr"/>
+      <c r="K15" s="36" t="n">
+        <v>0</v>
+      </c>
       <c r="L15" s="37" t="n"/>
       <c r="M15" s="37" t="n"/>
       <c r="N15" s="37" t="n"/>
@@ -2296,7 +2314,7 @@
         </is>
       </c>
       <c r="K16" s="42" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L16" s="43" t="n"/>
       <c r="M16" s="43" t="n"/>
@@ -2359,7 +2377,7 @@
         </is>
       </c>
       <c r="K17" s="36" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L17" s="37" t="n"/>
       <c r="M17" s="37" t="n"/>
@@ -2417,7 +2435,9 @@
         </is>
       </c>
       <c r="J18" s="41" t="n"/>
-      <c r="K18" s="42" t="inlineStr"/>
+      <c r="K18" s="42" t="n">
+        <v>0</v>
+      </c>
       <c r="L18" s="43" t="n"/>
       <c r="M18" s="43" t="n"/>
       <c r="N18" s="43" t="n"/>
@@ -2474,7 +2494,9 @@
         </is>
       </c>
       <c r="J19" s="35" t="n"/>
-      <c r="K19" s="36" t="inlineStr"/>
+      <c r="K19" s="36" t="n">
+        <v>0</v>
+      </c>
       <c r="L19" s="37" t="n"/>
       <c r="M19" s="37" t="n"/>
       <c r="N19" s="37" t="n"/>
@@ -2531,7 +2553,9 @@
         </is>
       </c>
       <c r="J20" s="41" t="n"/>
-      <c r="K20" s="42" t="inlineStr"/>
+      <c r="K20" s="42" t="n">
+        <v>0</v>
+      </c>
       <c r="L20" s="43" t="n"/>
       <c r="M20" s="43" t="n"/>
       <c r="N20" s="43" t="n"/>
@@ -2588,7 +2612,9 @@
         </is>
       </c>
       <c r="J21" s="35" t="n"/>
-      <c r="K21" s="36" t="inlineStr"/>
+      <c r="K21" s="36" t="n">
+        <v>0</v>
+      </c>
       <c r="L21" s="37" t="n"/>
       <c r="M21" s="37" t="n"/>
       <c r="N21" s="37" t="n"/>
@@ -2645,7 +2671,9 @@
         </is>
       </c>
       <c r="J22" s="41" t="n"/>
-      <c r="K22" s="42" t="inlineStr"/>
+      <c r="K22" s="42" t="n">
+        <v>0</v>
+      </c>
       <c r="L22" s="43" t="n"/>
       <c r="M22" s="43" t="n"/>
       <c r="N22" s="43" t="n"/>
@@ -2702,7 +2730,9 @@
         </is>
       </c>
       <c r="J23" s="35" t="n"/>
-      <c r="K23" s="36" t="inlineStr"/>
+      <c r="K23" s="36" t="n">
+        <v>0</v>
+      </c>
       <c r="L23" s="37" t="n"/>
       <c r="M23" s="37" t="n"/>
       <c r="N23" s="37" t="n"/>
@@ -2759,7 +2789,9 @@
         </is>
       </c>
       <c r="J24" s="41" t="n"/>
-      <c r="K24" s="42" t="inlineStr"/>
+      <c r="K24" s="42" t="n">
+        <v>0</v>
+      </c>
       <c r="L24" s="43" t="n"/>
       <c r="M24" s="43" t="n"/>
       <c r="N24" s="43" t="n"/>
@@ -2816,7 +2848,9 @@
         </is>
       </c>
       <c r="J25" s="35" t="n"/>
-      <c r="K25" s="36" t="inlineStr"/>
+      <c r="K25" s="36" t="n">
+        <v>0</v>
+      </c>
       <c r="L25" s="37" t="n"/>
       <c r="M25" s="37" t="n"/>
       <c r="N25" s="37" t="n"/>
@@ -2873,7 +2907,9 @@
         </is>
       </c>
       <c r="J26" s="41" t="n"/>
-      <c r="K26" s="42" t="inlineStr"/>
+      <c r="K26" s="42" t="n">
+        <v>0</v>
+      </c>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="43" t="n"/>
       <c r="N26" s="43" t="n"/>
@@ -2930,7 +2966,9 @@
         </is>
       </c>
       <c r="J27" s="35" t="n"/>
-      <c r="K27" s="36" t="inlineStr"/>
+      <c r="K27" s="36" t="n">
+        <v>0</v>
+      </c>
       <c r="L27" s="37" t="n"/>
       <c r="M27" s="37" t="n"/>
       <c r="N27" s="37" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
@@ -364,7 +364,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -618,6 +618,24 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="20" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -739,15 +757,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -761,46 +794,86 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -811,11 +884,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -830,31 +911,55 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -863,115 +968,196 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 상세컨셉 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 상세컨셉 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 3D/2D설계 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 3D/2D설계 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ BOM작성 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ BOM작성 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 가공품발주 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 가공품발주 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메뉴얼 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 메뉴얼 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 제안서 완료일
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 제안서 완료일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-05-15
 • 허용: 26-5-15, 260515, 2026.5.15 (자동 정규화)
 • 실제 제안서 작성·제출 완료된 날짜 기입
 • 비워두면 미완료 상태
 • 예정일이 아닌 ★실제 완료일★ 만 입력</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 설계 완료일 (3D/2D 설계 완료)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 설계 완료일 (3D/2D 설계 완료)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-06-30
 • 3D/2D 설계가 실제로 완료된 날짜
 • 비워두면 미완료
 • 예정일 아닌 실제 완료일</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 가공의뢰 입고일
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 가공의뢰 입고일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-07-10
 • 가공팀 의뢰분 또는 외주 가공품의
   ★실제 입고된 날짜★ 기입 (내부·외주 무관)
 • 비워두면: 대시보드 외주현황에 '진행중' 표시
 • 입고일 입력 시: '입고완료'로 자동 분류</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 작업 상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메모 (부서 자유 입력)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1295,7 +1481,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="93" t="inlineStr">
+      <c r="A1" s="99" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 설계팀 │ 2026</t>
         </is>
@@ -1322,7 +1508,7 @@
       <c r="U1" s="47" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="94" t="inlineStr">
+      <c r="A2" s="100" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 설계팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1346,9 +1532,9 @@
       <c r="R2" s="46" t="n"/>
       <c r="S2" s="46" t="n"/>
       <c r="T2" s="47" t="n"/>
-      <c r="U2" s="95" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 11:54</t>
+      <c r="U2" s="101" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:34</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
@@ -221,7 +221,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -360,11 +360,40 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -673,6 +702,17 @@
     <xf numFmtId="0" fontId="10" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1481,7 +1521,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="99" t="inlineStr">
+      <c r="A1" s="102" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 설계팀 │ 2026</t>
         </is>
@@ -1508,7 +1548,7 @@
       <c r="U1" s="47" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="100" t="inlineStr">
+      <c r="A2" s="103" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 설계팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1529,14 +1569,14 @@
       <c r="O2" s="46" t="n"/>
       <c r="P2" s="46" t="n"/>
       <c r="Q2" s="46" t="n"/>
-      <c r="R2" s="46" t="n"/>
-      <c r="S2" s="46" t="n"/>
-      <c r="T2" s="47" t="n"/>
-      <c r="U2" s="101" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:34</t>
-        </is>
-      </c>
+      <c r="R2" s="47" t="n"/>
+      <c r="S2" s="104" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:56</t>
+        </is>
+      </c>
+      <c r="T2" s="105" t="n"/>
+      <c r="U2" s="106" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="27" t="inlineStr">
@@ -3858,9 +3898,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="S2:U2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="Q5:Q28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
@@ -393,7 +393,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -713,6 +713,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -797,30 +806,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -834,86 +828,46 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PO유형 (발주 성격)
+        <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -924,19 +878,11 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 영업단계 (Sales Pipeline)
+        <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -951,55 +897,31 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 담당자
+        <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -1008,196 +930,140 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 상세컨셉 (세부항목 진척률)
+        <t>▣ 상세컨셉 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 3D/2D설계 (세부항목 진척률)
+        <t>▣ 3D/2D설계 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ BOM작성 (세부항목 진척률)
+        <t>▣ BOM작성 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 가공품발주 (세부항목 진척률)
+        <t>▣ 가공품발주 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 메뉴얼 (세부항목 진척률)
+        <t>▣ 메뉴얼 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 제안서 완료일
+        <t>▣ 제안서 완료일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-05-15
 • 허용: 26-5-15, 260515, 2026.5.15 (자동 정규화)
 • 실제 제안서 작성·제출 완료된 날짜 기입
 • 비워두면 미완료 상태
 • 예정일이 아닌 ★실제 완료일★ 만 입력</t>
-        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 설계 완료일 (3D/2D 설계 완료)
+        <t>▣ 설계 완료일 (3D/2D 설계 완료)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-06-30
 • 3D/2D 설계가 실제로 완료된 날짜
 • 비워두면 미완료
 • 예정일 아닌 실제 완료일</t>
-        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 가공의뢰 입고일
+        <t>▣ 가공의뢰 입고일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-07-10
 • 가공팀 의뢰분 또는 외주 가공품의
   ★실제 입고된 날짜★ 기입 (내부·외주 무관)
 • 비워두면: 대시보드 외주현황에 '진행중' 표시
 • 입고일 입력 시: '입고완료'로 자동 분류</t>
-        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 작업 상태
+        <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 메모 (부서 자유 입력)
+        <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -1508,20 +1374,20 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" style="68" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" style="68" min="12" max="12"/>
-    <col width="11" customWidth="1" style="68" min="13" max="13"/>
-    <col width="9" customWidth="1" style="68" min="14" max="14"/>
-    <col width="12" customWidth="1" style="68" min="15" max="15"/>
-    <col width="8" customWidth="1" style="68" min="16" max="16"/>
-    <col width="12" customWidth="1" style="68" min="17" max="17"/>
-    <col width="12" customWidth="1" style="68" min="18" max="18"/>
-    <col width="12" customWidth="1" style="68" min="19" max="19"/>
+    <col width="5" customWidth="1" style="68" min="12" max="12"/>
+    <col width="5" customWidth="1" style="68" min="13" max="13"/>
+    <col width="5" customWidth="1" style="68" min="14" max="14"/>
+    <col width="5" customWidth="1" style="68" min="15" max="15"/>
+    <col width="5" customWidth="1" style="68" min="16" max="16"/>
+    <col width="5" customWidth="1" style="68" min="17" max="17"/>
+    <col width="5" customWidth="1" style="68" min="18" max="18"/>
+    <col width="5" customWidth="1" style="68" min="19" max="19"/>
     <col width="10" customWidth="1" style="68" min="20" max="20"/>
     <col width="28" customWidth="1" style="68" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="102" t="inlineStr">
+      <c r="A1" s="107" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 설계팀 │ 2026</t>
         </is>
@@ -1548,7 +1414,7 @@
       <c r="U1" s="47" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="103" t="inlineStr">
+      <c r="A2" s="108" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 설계팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1570,13 +1436,13 @@
       <c r="P2" s="46" t="n"/>
       <c r="Q2" s="46" t="n"/>
       <c r="R2" s="47" t="n"/>
-      <c r="S2" s="104" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:56</t>
-        </is>
-      </c>
-      <c r="T2" s="105" t="n"/>
-      <c r="U2" s="106" t="n"/>
+      <c r="S2" s="109" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:27</t>
+        </is>
+      </c>
+      <c r="T2" s="46" t="n"/>
+      <c r="U2" s="47" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="27" t="inlineStr">
@@ -1743,22 +1609,26 @@
       </c>
       <c r="L4" s="32" t="inlineStr">
         <is>
-          <t>상세컨셉</t>
+          <t>상세컨
+셉</t>
         </is>
       </c>
       <c r="M4" s="32" t="inlineStr">
         <is>
-          <t>3D/2D설계</t>
+          <t>3D/
+2D설계</t>
         </is>
       </c>
       <c r="N4" s="32" t="inlineStr">
         <is>
-          <t>BOM작성</t>
+          <t>BOM
+작성</t>
         </is>
       </c>
       <c r="O4" s="32" t="inlineStr">
         <is>
-          <t>가공품발주</t>
+          <t>가공품
+발주</t>
         </is>
       </c>
       <c r="P4" s="32" t="inlineStr">
@@ -1991,7 +1861,7 @@
       </c>
       <c r="J7" s="35" t="n"/>
       <c r="K7" s="36" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L7" s="37" t="n">
         <v>1</v>
@@ -2064,7 +1934,7 @@
       </c>
       <c r="J8" s="41" t="n"/>
       <c r="K8" s="42" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L8" s="43" t="n"/>
       <c r="M8" s="43" t="n"/>
@@ -2122,8 +1992,10 @@
         </is>
       </c>
       <c r="J9" s="35" t="n"/>
-      <c r="K9" s="36" t="n">
-        <v>0</v>
+      <c r="K9" s="36" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L9" s="37" t="n"/>
       <c r="M9" s="37" t="n"/>
@@ -2182,7 +2054,7 @@
       </c>
       <c r="J10" s="41" t="n"/>
       <c r="K10" s="42" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L10" s="43" t="n"/>
       <c r="M10" s="43" t="n"/>
@@ -2240,8 +2112,10 @@
         </is>
       </c>
       <c r="J11" s="35" t="n"/>
-      <c r="K11" s="36" t="n">
-        <v>0</v>
+      <c r="K11" s="36" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L11" s="37" t="n"/>
       <c r="M11" s="37" t="n"/>
@@ -2299,8 +2173,10 @@
         </is>
       </c>
       <c r="J12" s="41" t="n"/>
-      <c r="K12" s="42" t="n">
-        <v>0</v>
+      <c r="K12" s="42" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L12" s="43" t="n"/>
       <c r="M12" s="43" t="n"/>
@@ -2359,7 +2235,7 @@
       </c>
       <c r="J13" s="35" t="n"/>
       <c r="K13" s="36" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L13" s="37" t="n"/>
       <c r="M13" s="37" t="n"/>
@@ -2417,8 +2293,10 @@
         </is>
       </c>
       <c r="J14" s="41" t="n"/>
-      <c r="K14" s="42" t="n">
-        <v>0</v>
+      <c r="K14" s="42" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L14" s="43" t="n"/>
       <c r="M14" s="43" t="n"/>
@@ -2476,8 +2354,10 @@
         </is>
       </c>
       <c r="J15" s="35" t="n"/>
-      <c r="K15" s="36" t="n">
-        <v>0</v>
+      <c r="K15" s="36" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L15" s="37" t="n"/>
       <c r="M15" s="37" t="n"/>
@@ -2539,8 +2419,10 @@
           <t>정민규</t>
         </is>
       </c>
-      <c r="K16" s="42" t="n">
-        <v>0</v>
+      <c r="K16" s="42" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L16" s="43" t="n"/>
       <c r="M16" s="43" t="n"/>
@@ -2602,8 +2484,10 @@
           <t>한재운</t>
         </is>
       </c>
-      <c r="K17" s="36" t="n">
-        <v>0</v>
+      <c r="K17" s="36" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L17" s="37" t="n"/>
       <c r="M17" s="37" t="n"/>
@@ -2661,8 +2545,10 @@
         </is>
       </c>
       <c r="J18" s="41" t="n"/>
-      <c r="K18" s="42" t="n">
-        <v>0</v>
+      <c r="K18" s="42" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L18" s="43" t="n"/>
       <c r="M18" s="43" t="n"/>
@@ -2720,8 +2606,10 @@
         </is>
       </c>
       <c r="J19" s="35" t="n"/>
-      <c r="K19" s="36" t="n">
-        <v>0</v>
+      <c r="K19" s="36" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L19" s="37" t="n"/>
       <c r="M19" s="37" t="n"/>
@@ -2779,8 +2667,10 @@
         </is>
       </c>
       <c r="J20" s="41" t="n"/>
-      <c r="K20" s="42" t="n">
-        <v>0</v>
+      <c r="K20" s="42" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L20" s="43" t="n"/>
       <c r="M20" s="43" t="n"/>
@@ -2838,8 +2728,10 @@
         </is>
       </c>
       <c r="J21" s="35" t="n"/>
-      <c r="K21" s="36" t="n">
-        <v>0</v>
+      <c r="K21" s="36" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L21" s="37" t="n"/>
       <c r="M21" s="37" t="n"/>
@@ -2897,8 +2789,10 @@
         </is>
       </c>
       <c r="J22" s="41" t="n"/>
-      <c r="K22" s="42" t="n">
-        <v>0</v>
+      <c r="K22" s="42" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L22" s="43" t="n"/>
       <c r="M22" s="43" t="n"/>
@@ -2956,8 +2850,10 @@
         </is>
       </c>
       <c r="J23" s="35" t="n"/>
-      <c r="K23" s="36" t="n">
-        <v>0</v>
+      <c r="K23" s="36" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L23" s="37" t="n"/>
       <c r="M23" s="37" t="n"/>
@@ -3015,8 +2911,10 @@
         </is>
       </c>
       <c r="J24" s="41" t="n"/>
-      <c r="K24" s="42" t="n">
-        <v>0</v>
+      <c r="K24" s="42" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L24" s="43" t="n"/>
       <c r="M24" s="43" t="n"/>
@@ -3074,8 +2972,10 @@
         </is>
       </c>
       <c r="J25" s="35" t="n"/>
-      <c r="K25" s="36" t="n">
-        <v>0</v>
+      <c r="K25" s="36" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L25" s="37" t="n"/>
       <c r="M25" s="37" t="n"/>
@@ -3133,8 +3033,10 @@
         </is>
       </c>
       <c r="J26" s="41" t="n"/>
-      <c r="K26" s="42" t="n">
-        <v>0</v>
+      <c r="K26" s="42" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="43" t="n"/>
@@ -3192,8 +3094,10 @@
         </is>
       </c>
       <c r="J27" s="35" t="n"/>
-      <c r="K27" s="36" t="n">
-        <v>0</v>
+      <c r="K27" s="36" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L27" s="37" t="n"/>
       <c r="M27" s="37" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
@@ -393,7 +393,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -713,6 +713,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -806,15 +815,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -828,46 +852,86 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -878,11 +942,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -897,31 +969,55 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -930,11 +1026,19 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 상세컨셉 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 상세컨셉 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -946,11 +1050,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 3D/2D설계 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 3D/2D설계 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -962,11 +1074,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ BOM작성 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ BOM작성 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -978,11 +1098,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 가공품발주 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 가공품발주 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -994,11 +1122,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메뉴얼 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 메뉴얼 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -1010,60 +1146,106 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 제안서 완료일
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 제안서 완료일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-05-15
 • 허용: 26-5-15, 260515, 2026.5.15 (자동 정규화)
 • 실제 제안서 작성·제출 완료된 날짜 기입
 • 비워두면 미완료 상태
 • 예정일이 아닌 ★실제 완료일★ 만 입력</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 설계 완료일 (3D/2D 설계 완료)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 설계 완료일 (3D/2D 설계 완료)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-06-30
 • 3D/2D 설계가 실제로 완료된 날짜
 • 비워두면 미완료
 • 예정일 아닌 실제 완료일</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 가공의뢰 입고일
-★ 날짜 입력 (% 아님 ⚠️)
-• 형식: YYYY-MM-DD  예: 2026-07-10
-• 가공팀 의뢰분 또는 외주 가공품의
-  ★실제 입고된 날짜★ 기입 (내부·외주 무관)
-• 비워두면: 대시보드 외주현황에 '진행중' 표시
-• 입고일 입력 시: '입고완료'로 자동 분류</t>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 의뢰입고일 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 작업 상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메모 (부서 자유 입력)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1374,20 +1556,20 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" style="68" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" style="68" min="12" max="12"/>
-    <col width="5" customWidth="1" style="68" min="13" max="13"/>
-    <col width="5" customWidth="1" style="68" min="14" max="14"/>
-    <col width="5" customWidth="1" style="68" min="15" max="15"/>
-    <col width="5" customWidth="1" style="68" min="16" max="16"/>
-    <col width="5" customWidth="1" style="68" min="17" max="17"/>
-    <col width="5" customWidth="1" style="68" min="18" max="18"/>
-    <col width="5" customWidth="1" style="68" min="19" max="19"/>
+    <col width="7" customWidth="1" style="68" min="12" max="12"/>
+    <col width="7" customWidth="1" style="68" min="13" max="13"/>
+    <col width="7" customWidth="1" style="68" min="14" max="14"/>
+    <col width="7" customWidth="1" style="68" min="15" max="15"/>
+    <col width="7" customWidth="1" style="68" min="16" max="16"/>
+    <col width="7" customWidth="1" style="68" min="17" max="17"/>
+    <col width="7" customWidth="1" style="68" min="18" max="18"/>
+    <col width="7" customWidth="1" style="68" min="19" max="19"/>
     <col width="10" customWidth="1" style="68" min="20" max="20"/>
     <col width="28" customWidth="1" style="68" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="107" t="inlineStr">
+      <c r="A1" s="110" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 설계팀 │ 2026</t>
         </is>
@@ -1414,7 +1596,7 @@
       <c r="U1" s="47" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="108" t="inlineStr">
+      <c r="A2" s="111" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 설계팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1436,9 +1618,9 @@
       <c r="P2" s="46" t="n"/>
       <c r="Q2" s="46" t="n"/>
       <c r="R2" s="47" t="n"/>
-      <c r="S2" s="109" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:27</t>
+      <c r="S2" s="112" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:39</t>
         </is>
       </c>
       <c r="T2" s="46" t="n"/>
@@ -1609,14 +1791,14 @@
       </c>
       <c r="L4" s="32" t="inlineStr">
         <is>
-          <t>상세컨
-셉</t>
+          <t>상세
+컨셉</t>
         </is>
       </c>
       <c r="M4" s="32" t="inlineStr">
         <is>
-          <t>3D/
-2D설계</t>
+          <t>3D/2D
+설계</t>
         </is>
       </c>
       <c r="N4" s="32" t="inlineStr">
@@ -1650,7 +1832,7 @@
       </c>
       <c r="S4" s="83" t="inlineStr">
         <is>
-          <t>가공의뢰
+          <t>의뢰
 입고일</t>
         </is>
       </c>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
@@ -393,7 +393,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -713,6 +713,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -815,30 +824,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -852,86 +846,46 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PO유형 (발주 성격)
+        <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -942,19 +896,11 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 영업단계 (Sales Pipeline)
+        <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -969,55 +915,31 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 담당자
+        <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -1026,19 +948,11 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 상세컨셉 (세부항목 진척률)
+        <t>▣ 상세컨셉 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -1050,19 +964,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 3D/2D설계 (세부항목 진척률)
+        <t>▣ 3D/2D설계 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -1074,19 +980,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ BOM작성 (세부항목 진척률)
+        <t>▣ BOM작성 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -1098,19 +996,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 가공품발주 (세부항목 진척률)
+        <t>▣ 가공품발주 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -1122,19 +1012,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 메뉴얼 (세부항목 진척률)
+        <t>▣ 메뉴얼 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -1146,106 +1028,75 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 제안서 완료일
+        <t>▣ 제안서 완료일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-05-15
 • 허용: 26-5-15, 260515, 2026.5.15 (자동 정규화)
 • 실제 제안서 작성·제출 완료된 날짜 기입
 • 비워두면 미완료 상태
 • 예정일이 아닌 ★실제 완료일★ 만 입력</t>
-        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 설계 완료일 (3D/2D 설계 완료)
+        <t>▣ 설계 완료일 (3D/2D 설계 완료)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-06-30
 • 3D/2D 설계가 실제로 완료된 날짜
 • 비워두면 미완료
 • 예정일 아닌 실제 완료일</t>
-        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 의뢰입고일 (세부항목 진척률)
-★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
-  또는 0~100 정수도 허용 (예: 50, 100)
-📋 입력값 의미:
-  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
-           — 부서 진척률 평균에서 ★분모 제외★
-  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
-  ▸ 0.5   → 50% 진행 중
-  ▸ 1.0   → 100% 완료
-💡 부서장·담당자가 매주 진척률 갱신
-💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
+        <t>▣ 의뢰 입고예정일 (가공의뢰 후 예정)
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• 가공의뢰 발주 시 외부업체와 약속한
+  ★입고 완료 예정일★ 기입
+📋 운영:
+  ▸ 의뢰 시 예정일 입력
+  ▸ 실제 입고일과 비교 → 지연 여부 추적
+  ▸ 비워두면: 미발주 또는 일정 미정</t>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 작업 상태
+        <t>▣ 의뢰 입고일 (가공의뢰 결과)
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD
+• 가공의뢰한 부품·가공품이
+  ★실제 입고된 날짜★ 기입
+📋 의뢰예정일과 비교:
+  ▸ 입고일 ≤ 예정일 → 정시
+  ▸ 입고일 &gt; 예정일 → 지연
+  ▸ 입고일 = 빈 칸  → 미입고 (진행중)</t>
+      </text>
+    </comment>
+    <comment ref="U4" authorId="0" shapeId="0">
+      <text>
+        <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
-        </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0" shapeId="0">
+    <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 메모 (부서 자유 입력)
+        <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -1542,7 +1393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U57"/>
+  <dimension ref="A1:V57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1564,12 +1415,13 @@
     <col width="7" customWidth="1" style="68" min="17" max="17"/>
     <col width="7" customWidth="1" style="68" min="18" max="18"/>
     <col width="7" customWidth="1" style="68" min="19" max="19"/>
-    <col width="10" customWidth="1" style="68" min="20" max="20"/>
-    <col width="28" customWidth="1" style="68" min="21" max="21"/>
+    <col width="7" customWidth="1" style="68" min="20" max="20"/>
+    <col width="10" customWidth="1" style="68" min="21" max="21"/>
+    <col width="28" customWidth="1" style="68" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="110" t="inlineStr">
+      <c r="A1" s="113" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 설계팀 │ 2026</t>
         </is>
@@ -1593,10 +1445,11 @@
       <c r="R1" s="46" t="n"/>
       <c r="S1" s="46" t="n"/>
       <c r="T1" s="46" t="n"/>
-      <c r="U1" s="47" t="n"/>
+      <c r="U1" s="46" t="n"/>
+      <c r="V1" s="47" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="111" t="inlineStr">
+      <c r="A2" s="114" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 설계팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1617,14 +1470,15 @@
       <c r="O2" s="46" t="n"/>
       <c r="P2" s="46" t="n"/>
       <c r="Q2" s="46" t="n"/>
-      <c r="R2" s="47" t="n"/>
-      <c r="S2" s="112" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:39</t>
-        </is>
-      </c>
-      <c r="T2" s="46" t="n"/>
-      <c r="U2" s="47" t="n"/>
+      <c r="R2" s="46" t="n"/>
+      <c r="S2" s="47" t="n"/>
+      <c r="T2" s="115" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:47</t>
+        </is>
+      </c>
+      <c r="U2" s="46" t="n"/>
+      <c r="V2" s="47" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="27" t="inlineStr">
@@ -1722,12 +1576,17 @@
           <t>PO후입력</t>
         </is>
       </c>
-      <c r="T3" s="28" t="inlineStr">
+      <c r="T3" s="29" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="U3" s="28" t="inlineStr">
         <is>
           <t>✏선택▼</t>
         </is>
       </c>
-      <c r="U3" s="29" t="inlineStr">
+      <c r="V3" s="29" t="inlineStr">
         <is>
           <t>✏메모</t>
         </is>
@@ -1833,15 +1692,21 @@
       <c r="S4" s="83" t="inlineStr">
         <is>
           <t>의뢰
+예정일</t>
+        </is>
+      </c>
+      <c r="T4" s="83" t="inlineStr">
+        <is>
+          <t>의뢰
 입고일</t>
         </is>
       </c>
-      <c r="T4" s="32" t="inlineStr">
+      <c r="U4" s="32" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="U4" s="32" t="inlineStr">
+      <c r="V4" s="32" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1922,7 +1787,8 @@
           <t>진행중</t>
         </is>
       </c>
-      <c r="U5" s="38" t="n"/>
+      <c r="U5" s="35" t="n"/>
+      <c r="V5" s="38" t="n"/>
     </row>
     <row r="6" ht="22.05" customHeight="1">
       <c r="A6" s="39" t="n">
@@ -1995,7 +1861,8 @@
           <t>진행중</t>
         </is>
       </c>
-      <c r="U6" s="44" t="n"/>
+      <c r="U6" s="41" t="n"/>
+      <c r="V6" s="44" t="n"/>
     </row>
     <row r="7" ht="22.05" customHeight="1">
       <c r="A7" s="33" t="n">
@@ -2068,7 +1935,8 @@
           <t>진행중</t>
         </is>
       </c>
-      <c r="U7" s="38" t="n"/>
+      <c r="U7" s="35" t="n"/>
+      <c r="V7" s="38" t="n"/>
     </row>
     <row r="8" ht="22.05" customHeight="1">
       <c r="A8" s="39" t="n">
@@ -2127,7 +1995,8 @@
       <c r="R8" s="41" t="n"/>
       <c r="S8" s="41" t="n"/>
       <c r="T8" s="41" t="n"/>
-      <c r="U8" s="44" t="n"/>
+      <c r="U8" s="41" t="n"/>
+      <c r="V8" s="44" t="n"/>
     </row>
     <row r="9" ht="22.05" customHeight="1">
       <c r="A9" s="33" t="n">
@@ -2188,7 +2057,8 @@
       <c r="R9" s="35" t="n"/>
       <c r="S9" s="35" t="n"/>
       <c r="T9" s="35" t="n"/>
-      <c r="U9" s="38" t="n"/>
+      <c r="U9" s="35" t="n"/>
+      <c r="V9" s="38" t="n"/>
     </row>
     <row r="10" ht="22.05" customHeight="1">
       <c r="A10" s="39" t="n">
@@ -2247,7 +2117,8 @@
       <c r="R10" s="41" t="n"/>
       <c r="S10" s="41" t="n"/>
       <c r="T10" s="41" t="n"/>
-      <c r="U10" s="44" t="n"/>
+      <c r="U10" s="41" t="n"/>
+      <c r="V10" s="44" t="n"/>
     </row>
     <row r="11" ht="22.05" customHeight="1">
       <c r="A11" s="33" t="n">
@@ -2308,7 +2179,8 @@
       <c r="R11" s="35" t="n"/>
       <c r="S11" s="35" t="n"/>
       <c r="T11" s="35" t="n"/>
-      <c r="U11" s="38" t="n"/>
+      <c r="U11" s="35" t="n"/>
+      <c r="V11" s="38" t="n"/>
     </row>
     <row r="12" ht="22.05" customHeight="1">
       <c r="A12" s="39" t="n">
@@ -2369,7 +2241,8 @@
       <c r="R12" s="41" t="n"/>
       <c r="S12" s="41" t="n"/>
       <c r="T12" s="41" t="n"/>
-      <c r="U12" s="44" t="n"/>
+      <c r="U12" s="41" t="n"/>
+      <c r="V12" s="44" t="n"/>
     </row>
     <row r="13" ht="22.05" customHeight="1">
       <c r="A13" s="33" t="n">
@@ -2428,7 +2301,8 @@
       <c r="R13" s="35" t="n"/>
       <c r="S13" s="35" t="n"/>
       <c r="T13" s="35" t="n"/>
-      <c r="U13" s="38" t="n"/>
+      <c r="U13" s="35" t="n"/>
+      <c r="V13" s="38" t="n"/>
     </row>
     <row r="14" ht="22.05" customHeight="1">
       <c r="A14" s="39" t="n">
@@ -2489,7 +2363,8 @@
       <c r="R14" s="41" t="n"/>
       <c r="S14" s="41" t="n"/>
       <c r="T14" s="41" t="n"/>
-      <c r="U14" s="44" t="n"/>
+      <c r="U14" s="41" t="n"/>
+      <c r="V14" s="44" t="n"/>
     </row>
     <row r="15" ht="22.05" customHeight="1">
       <c r="A15" s="33" t="n">
@@ -2550,7 +2425,8 @@
       <c r="R15" s="35" t="n"/>
       <c r="S15" s="35" t="n"/>
       <c r="T15" s="35" t="n"/>
-      <c r="U15" s="38" t="n"/>
+      <c r="U15" s="35" t="n"/>
+      <c r="V15" s="38" t="n"/>
     </row>
     <row r="16" ht="22.05" customHeight="1">
       <c r="A16" s="39" t="n">
@@ -2615,7 +2491,8 @@
       <c r="R16" s="41" t="n"/>
       <c r="S16" s="41" t="n"/>
       <c r="T16" s="41" t="n"/>
-      <c r="U16" s="44" t="n"/>
+      <c r="U16" s="41" t="n"/>
+      <c r="V16" s="44" t="n"/>
     </row>
     <row r="17" ht="22.05" customHeight="1">
       <c r="A17" s="33" t="n">
@@ -2680,7 +2557,8 @@
       <c r="R17" s="35" t="n"/>
       <c r="S17" s="35" t="n"/>
       <c r="T17" s="35" t="n"/>
-      <c r="U17" s="38" t="n"/>
+      <c r="U17" s="35" t="n"/>
+      <c r="V17" s="38" t="n"/>
     </row>
     <row r="18" ht="22.05" customHeight="1">
       <c r="A18" s="39" t="n">
@@ -2741,7 +2619,8 @@
       <c r="R18" s="41" t="n"/>
       <c r="S18" s="41" t="n"/>
       <c r="T18" s="41" t="n"/>
-      <c r="U18" s="44" t="n"/>
+      <c r="U18" s="41" t="n"/>
+      <c r="V18" s="44" t="n"/>
     </row>
     <row r="19" ht="22.05" customHeight="1">
       <c r="A19" s="33" t="n">
@@ -2802,7 +2681,8 @@
       <c r="R19" s="35" t="n"/>
       <c r="S19" s="35" t="n"/>
       <c r="T19" s="35" t="n"/>
-      <c r="U19" s="38" t="n"/>
+      <c r="U19" s="35" t="n"/>
+      <c r="V19" s="38" t="n"/>
     </row>
     <row r="20" ht="22.05" customHeight="1">
       <c r="A20" s="39" t="n">
@@ -2863,7 +2743,8 @@
       <c r="R20" s="41" t="n"/>
       <c r="S20" s="41" t="n"/>
       <c r="T20" s="41" t="n"/>
-      <c r="U20" s="44" t="n"/>
+      <c r="U20" s="41" t="n"/>
+      <c r="V20" s="44" t="n"/>
     </row>
     <row r="21" ht="22.05" customHeight="1">
       <c r="A21" s="33" t="n">
@@ -2924,7 +2805,8 @@
       <c r="R21" s="35" t="n"/>
       <c r="S21" s="35" t="n"/>
       <c r="T21" s="35" t="n"/>
-      <c r="U21" s="38" t="n"/>
+      <c r="U21" s="35" t="n"/>
+      <c r="V21" s="38" t="n"/>
     </row>
     <row r="22" ht="22.05" customHeight="1">
       <c r="A22" s="39" t="n">
@@ -2985,7 +2867,8 @@
       <c r="R22" s="41" t="n"/>
       <c r="S22" s="41" t="n"/>
       <c r="T22" s="41" t="n"/>
-      <c r="U22" s="44" t="n"/>
+      <c r="U22" s="41" t="n"/>
+      <c r="V22" s="44" t="n"/>
     </row>
     <row r="23" ht="22.05" customHeight="1">
       <c r="A23" s="33" t="n">
@@ -3046,7 +2929,8 @@
       <c r="R23" s="35" t="n"/>
       <c r="S23" s="35" t="n"/>
       <c r="T23" s="35" t="n"/>
-      <c r="U23" s="38" t="n"/>
+      <c r="U23" s="35" t="n"/>
+      <c r="V23" s="38" t="n"/>
     </row>
     <row r="24" ht="22.05" customHeight="1">
       <c r="A24" s="39" t="n">
@@ -3107,7 +2991,8 @@
       <c r="R24" s="41" t="n"/>
       <c r="S24" s="41" t="n"/>
       <c r="T24" s="41" t="n"/>
-      <c r="U24" s="44" t="n"/>
+      <c r="U24" s="41" t="n"/>
+      <c r="V24" s="44" t="n"/>
     </row>
     <row r="25" ht="22.05" customHeight="1">
       <c r="A25" s="33" t="n">
@@ -3168,7 +3053,8 @@
       <c r="R25" s="35" t="n"/>
       <c r="S25" s="35" t="n"/>
       <c r="T25" s="35" t="n"/>
-      <c r="U25" s="38" t="n"/>
+      <c r="U25" s="35" t="n"/>
+      <c r="V25" s="38" t="n"/>
     </row>
     <row r="26" ht="22.05" customHeight="1">
       <c r="A26" s="39" t="n">
@@ -3229,7 +3115,8 @@
       <c r="R26" s="41" t="n"/>
       <c r="S26" s="41" t="n"/>
       <c r="T26" s="41" t="n"/>
-      <c r="U26" s="44" t="n"/>
+      <c r="U26" s="41" t="n"/>
+      <c r="V26" s="44" t="n"/>
     </row>
     <row r="27" ht="22.05" customHeight="1">
       <c r="A27" s="33" t="n">
@@ -3290,7 +3177,8 @@
       <c r="R27" s="35" t="n"/>
       <c r="S27" s="35" t="n"/>
       <c r="T27" s="35" t="n"/>
-      <c r="U27" s="38" t="n"/>
+      <c r="U27" s="35" t="n"/>
+      <c r="V27" s="38" t="n"/>
     </row>
     <row r="28" ht="22.05" customHeight="1">
       <c r="A28" s="39" t="n"/>
@@ -3313,7 +3201,8 @@
       <c r="R28" s="41" t="n"/>
       <c r="S28" s="41" t="n"/>
       <c r="T28" s="41" t="n"/>
-      <c r="U28" s="44" t="n"/>
+      <c r="U28" s="41" t="n"/>
+      <c r="V28" s="44" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="33" t="n"/>
@@ -3336,7 +3225,8 @@
       <c r="R29" s="35" t="n"/>
       <c r="S29" s="35" t="n"/>
       <c r="T29" s="35" t="n"/>
-      <c r="U29" s="38" t="n"/>
+      <c r="U29" s="35" t="n"/>
+      <c r="V29" s="38" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="39" t="n"/>
@@ -3359,7 +3249,8 @@
       <c r="R30" s="41" t="n"/>
       <c r="S30" s="41" t="n"/>
       <c r="T30" s="41" t="n"/>
-      <c r="U30" s="44" t="n"/>
+      <c r="U30" s="41" t="n"/>
+      <c r="V30" s="44" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="33" t="n"/>
@@ -3382,7 +3273,8 @@
       <c r="R31" s="35" t="n"/>
       <c r="S31" s="35" t="n"/>
       <c r="T31" s="35" t="n"/>
-      <c r="U31" s="38" t="n"/>
+      <c r="U31" s="35" t="n"/>
+      <c r="V31" s="38" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="39" t="n"/>
@@ -3405,7 +3297,8 @@
       <c r="R32" s="41" t="n"/>
       <c r="S32" s="41" t="n"/>
       <c r="T32" s="41" t="n"/>
-      <c r="U32" s="44" t="n"/>
+      <c r="U32" s="41" t="n"/>
+      <c r="V32" s="44" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="33" t="n"/>
@@ -3428,7 +3321,8 @@
       <c r="R33" s="35" t="n"/>
       <c r="S33" s="35" t="n"/>
       <c r="T33" s="35" t="n"/>
-      <c r="U33" s="38" t="n"/>
+      <c r="U33" s="35" t="n"/>
+      <c r="V33" s="38" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="39" t="n"/>
@@ -3451,7 +3345,8 @@
       <c r="R34" s="41" t="n"/>
       <c r="S34" s="41" t="n"/>
       <c r="T34" s="41" t="n"/>
-      <c r="U34" s="44" t="n"/>
+      <c r="U34" s="41" t="n"/>
+      <c r="V34" s="44" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="33" t="n"/>
@@ -3474,7 +3369,8 @@
       <c r="R35" s="35" t="n"/>
       <c r="S35" s="35" t="n"/>
       <c r="T35" s="35" t="n"/>
-      <c r="U35" s="38" t="n"/>
+      <c r="U35" s="35" t="n"/>
+      <c r="V35" s="38" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="39" t="n"/>
@@ -3497,7 +3393,8 @@
       <c r="R36" s="41" t="n"/>
       <c r="S36" s="41" t="n"/>
       <c r="T36" s="41" t="n"/>
-      <c r="U36" s="44" t="n"/>
+      <c r="U36" s="41" t="n"/>
+      <c r="V36" s="44" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="33" t="n"/>
@@ -3520,7 +3417,8 @@
       <c r="R37" s="35" t="n"/>
       <c r="S37" s="35" t="n"/>
       <c r="T37" s="35" t="n"/>
-      <c r="U37" s="38" t="n"/>
+      <c r="U37" s="35" t="n"/>
+      <c r="V37" s="38" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="39" t="n"/>
@@ -3543,7 +3441,8 @@
       <c r="R38" s="41" t="n"/>
       <c r="S38" s="41" t="n"/>
       <c r="T38" s="41" t="n"/>
-      <c r="U38" s="44" t="n"/>
+      <c r="U38" s="41" t="n"/>
+      <c r="V38" s="44" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="33" t="n"/>
@@ -3566,7 +3465,8 @@
       <c r="R39" s="35" t="n"/>
       <c r="S39" s="35" t="n"/>
       <c r="T39" s="35" t="n"/>
-      <c r="U39" s="38" t="n"/>
+      <c r="U39" s="35" t="n"/>
+      <c r="V39" s="38" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="39" t="n"/>
@@ -3589,7 +3489,8 @@
       <c r="R40" s="41" t="n"/>
       <c r="S40" s="41" t="n"/>
       <c r="T40" s="41" t="n"/>
-      <c r="U40" s="44" t="n"/>
+      <c r="U40" s="41" t="n"/>
+      <c r="V40" s="44" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="33" t="n"/>
@@ -3612,7 +3513,8 @@
       <c r="R41" s="35" t="n"/>
       <c r="S41" s="35" t="n"/>
       <c r="T41" s="35" t="n"/>
-      <c r="U41" s="38" t="n"/>
+      <c r="U41" s="35" t="n"/>
+      <c r="V41" s="38" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="39" t="n"/>
@@ -3635,7 +3537,8 @@
       <c r="R42" s="41" t="n"/>
       <c r="S42" s="41" t="n"/>
       <c r="T42" s="41" t="n"/>
-      <c r="U42" s="44" t="n"/>
+      <c r="U42" s="41" t="n"/>
+      <c r="V42" s="44" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="33" t="n"/>
@@ -3658,7 +3561,8 @@
       <c r="R43" s="35" t="n"/>
       <c r="S43" s="35" t="n"/>
       <c r="T43" s="35" t="n"/>
-      <c r="U43" s="38" t="n"/>
+      <c r="U43" s="35" t="n"/>
+      <c r="V43" s="38" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="39" t="n"/>
@@ -3681,7 +3585,8 @@
       <c r="R44" s="41" t="n"/>
       <c r="S44" s="41" t="n"/>
       <c r="T44" s="41" t="n"/>
-      <c r="U44" s="44" t="n"/>
+      <c r="U44" s="41" t="n"/>
+      <c r="V44" s="44" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="33" t="n"/>
@@ -3704,7 +3609,8 @@
       <c r="R45" s="35" t="n"/>
       <c r="S45" s="35" t="n"/>
       <c r="T45" s="35" t="n"/>
-      <c r="U45" s="38" t="n"/>
+      <c r="U45" s="35" t="n"/>
+      <c r="V45" s="38" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="39" t="n"/>
@@ -3727,7 +3633,8 @@
       <c r="R46" s="41" t="n"/>
       <c r="S46" s="41" t="n"/>
       <c r="T46" s="41" t="n"/>
-      <c r="U46" s="44" t="n"/>
+      <c r="U46" s="41" t="n"/>
+      <c r="V46" s="44" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="33" t="n"/>
@@ -3750,7 +3657,8 @@
       <c r="R47" s="35" t="n"/>
       <c r="S47" s="35" t="n"/>
       <c r="T47" s="35" t="n"/>
-      <c r="U47" s="38" t="n"/>
+      <c r="U47" s="35" t="n"/>
+      <c r="V47" s="38" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="39" t="n"/>
@@ -3773,7 +3681,8 @@
       <c r="R48" s="41" t="n"/>
       <c r="S48" s="41" t="n"/>
       <c r="T48" s="41" t="n"/>
-      <c r="U48" s="44" t="n"/>
+      <c r="U48" s="41" t="n"/>
+      <c r="V48" s="44" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="33" t="n"/>
@@ -3796,7 +3705,8 @@
       <c r="R49" s="35" t="n"/>
       <c r="S49" s="35" t="n"/>
       <c r="T49" s="35" t="n"/>
-      <c r="U49" s="38" t="n"/>
+      <c r="U49" s="35" t="n"/>
+      <c r="V49" s="38" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="39" t="n"/>
@@ -3819,7 +3729,8 @@
       <c r="R50" s="41" t="n"/>
       <c r="S50" s="41" t="n"/>
       <c r="T50" s="41" t="n"/>
-      <c r="U50" s="44" t="n"/>
+      <c r="U50" s="41" t="n"/>
+      <c r="V50" s="44" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="33" t="n"/>
@@ -3842,7 +3753,8 @@
       <c r="R51" s="35" t="n"/>
       <c r="S51" s="35" t="n"/>
       <c r="T51" s="35" t="n"/>
-      <c r="U51" s="38" t="n"/>
+      <c r="U51" s="35" t="n"/>
+      <c r="V51" s="38" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="39" t="n"/>
@@ -3865,7 +3777,8 @@
       <c r="R52" s="41" t="n"/>
       <c r="S52" s="41" t="n"/>
       <c r="T52" s="41" t="n"/>
-      <c r="U52" s="44" t="n"/>
+      <c r="U52" s="41" t="n"/>
+      <c r="V52" s="44" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="33" t="n"/>
@@ -3888,7 +3801,8 @@
       <c r="R53" s="35" t="n"/>
       <c r="S53" s="35" t="n"/>
       <c r="T53" s="35" t="n"/>
-      <c r="U53" s="38" t="n"/>
+      <c r="U53" s="35" t="n"/>
+      <c r="V53" s="38" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="39" t="n"/>
@@ -3911,7 +3825,8 @@
       <c r="R54" s="41" t="n"/>
       <c r="S54" s="41" t="n"/>
       <c r="T54" s="41" t="n"/>
-      <c r="U54" s="44" t="n"/>
+      <c r="U54" s="41" t="n"/>
+      <c r="V54" s="44" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="33" t="n"/>
@@ -3934,7 +3849,8 @@
       <c r="R55" s="35" t="n"/>
       <c r="S55" s="35" t="n"/>
       <c r="T55" s="35" t="n"/>
-      <c r="U55" s="38" t="n"/>
+      <c r="U55" s="35" t="n"/>
+      <c r="V55" s="38" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="39" t="n"/>
@@ -3957,7 +3873,8 @@
       <c r="R56" s="41" t="n"/>
       <c r="S56" s="41" t="n"/>
       <c r="T56" s="41" t="n"/>
-      <c r="U56" s="44" t="n"/>
+      <c r="U56" s="41" t="n"/>
+      <c r="V56" s="44" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="33" t="n"/>
@@ -3980,14 +3897,15 @@
       <c r="R57" s="35" t="n"/>
       <c r="S57" s="35" t="n"/>
       <c r="T57" s="35" t="n"/>
-      <c r="U57" s="38" t="n"/>
+      <c r="U57" s="35" t="n"/>
+      <c r="V57" s="38" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="3">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="S2:U2"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A2:S2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="Q5:Q28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
@@ -393,7 +393,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -713,6 +713,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -824,15 +833,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -846,46 +870,86 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -896,11 +960,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -915,31 +987,55 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -948,11 +1044,19 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 상세컨셉 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 상세컨셉 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -964,11 +1068,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 3D/2D설계 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 3D/2D설계 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -980,11 +1092,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ BOM작성 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ BOM작성 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -996,11 +1116,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 가공품발주 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 가공품발주 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -1012,11 +1140,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메뉴얼 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 메뉴얼 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -1028,32 +1164,56 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 제안서 완료일
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 제안서 완료일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-05-15
 • 허용: 26-5-15, 260515, 2026.5.15 (자동 정규화)
 • 실제 제안서 작성·제출 완료된 날짜 기입
 • 비워두면 미완료 상태
 • 예정일이 아닌 ★실제 완료일★ 만 입력</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 설계 완료일 (3D/2D 설계 완료)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 설계 완료일 (3D/2D 설계 완료)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-06-30
 • 3D/2D 설계가 실제로 완료된 날짜
 • 비워두면 미완료
 • 예정일 아닌 실제 완료일</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 의뢰 입고예정일 (가공의뢰 후 예정)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 의뢰 입고예정일 (가공의뢰 후 예정)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-07-15
 • 가공의뢰 발주 시 외부업체와 약속한
@@ -1062,11 +1222,19 @@
   ▸ 의뢰 시 예정일 입력
   ▸ 실제 입고일과 비교 → 지연 여부 추적
   ▸ 비워두면: 미발주 또는 일정 미정</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 의뢰 입고일 (가공의뢰 결과)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 의뢰 입고일 (가공의뢰 결과)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD
 • 가공의뢰한 부품·가공품이
@@ -1075,28 +1243,45 @@
   ▸ 입고일 ≤ 예정일 → 정시
   ▸ 입고일 &gt; 예정일 → 지연
   ▸ 입고일 = 빈 칸  → 미입고 (진행중)</t>
+        </r>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 작업 상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메모 (부서 자유 입력)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1421,7 +1606,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="113" t="inlineStr">
+      <c r="A1" s="116" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 설계팀 │ 2026</t>
         </is>
@@ -1449,7 +1634,7 @@
       <c r="V1" s="47" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="114" t="inlineStr">
+      <c r="A2" s="117" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 설계팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1472,9 +1657,9 @@
       <c r="Q2" s="46" t="n"/>
       <c r="R2" s="46" t="n"/>
       <c r="S2" s="47" t="n"/>
-      <c r="T2" s="115" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:47</t>
+      <c r="T2" s="118" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 14:00</t>
         </is>
       </c>
       <c r="U2" s="46" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
@@ -393,7 +393,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -713,6 +713,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1080,6 +1098,28 @@
             <family val="3"/>
             <charset val="129"/>
           </rPr>
+          <t>▣ 상세컨셉 — 완료 예정일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• 상세컨셉 작업의 ★완료 예정일★ 기입
+📋 운영:
+  ▸ 좌측 셀 = 진척률(%)
+  ▸ 이 셀  = 상세컨셉 완료 목표일
+  ▸ 진척률과 비교 → 일정 대비 진행도 추적
+  ▸ 예: 7/15까지 100% 목표인데 7/10 현재 50% → 일정 빠름
+• 비워두면: 일정 미정 또는 해당없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
           <t>▣ 3D/2D설계 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
@@ -1095,7 +1135,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0" shapeId="0">
+    <comment ref="O4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 3D/2D설계 — 완료 예정일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• 3D/2D설계 작업의 ★완료 예정일★ 기입
+📋 운영:
+  ▸ 좌측 셀 = 진척률(%)
+  ▸ 이 셀  = 3D/2D설계 완료 목표일
+  ▸ 진척률과 비교 → 일정 대비 진행도 추적
+  ▸ 예: 7/15까지 100% 목표인데 7/10 현재 50% → 일정 빠름
+• 비워두면: 일정 미정 또는 해당없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1119,7 +1181,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="O4" authorId="0" shapeId="0">
+    <comment ref="Q4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ BOM작성 — 완료 예정일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• BOM작성 작업의 ★완료 예정일★ 기입
+📋 운영:
+  ▸ 좌측 셀 = 진척률(%)
+  ▸ 이 셀  = BOM작성 완료 목표일
+  ▸ 진척률과 비교 → 일정 대비 진행도 추적
+  ▸ 예: 7/15까지 100% 목표인데 7/10 현재 50% → 일정 빠름
+• 비워두면: 일정 미정 또는 해당없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1143,7 +1227,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="P4" authorId="0" shapeId="0">
+    <comment ref="S4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 가공품발주 — 완료 예정일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• 가공품발주 작업의 ★완료 예정일★ 기입
+📋 운영:
+  ▸ 좌측 셀 = 진척률(%)
+  ▸ 이 셀  = 가공품발주 완료 목표일
+  ▸ 진척률과 비교 → 일정 대비 진행도 추적
+  ▸ 예: 7/15까지 100% 목표인데 7/10 현재 50% → 일정 빠름
+• 비워두면: 일정 미정 또는 해당없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1167,7 +1273,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0" shapeId="0">
+    <comment ref="U4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 메뉴얼 — 완료 예정일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• 메뉴얼 작업의 ★완료 예정일★ 기입
+📋 운영:
+  ▸ 좌측 셀 = 진척률(%)
+  ▸ 이 셀  = 메뉴얼 완료 목표일
+  ▸ 진척률과 비교 → 일정 대비 진행도 추적
+  ▸ 예: 7/15까지 100% 목표인데 7/10 현재 50% → 일정 빠름
+• 비워두면: 일정 미정 또는 해당없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1186,7 +1314,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R4" authorId="0" shapeId="0">
+    <comment ref="W4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1204,7 +1332,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="X4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1225,7 +1353,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T4" authorId="0" shapeId="0">
+    <comment ref="Y4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1246,7 +1374,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0" shapeId="0">
+    <comment ref="Z4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1265,7 +1393,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V4" authorId="0" shapeId="0">
+    <comment ref="AA4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1578,7 +1706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V57"/>
+  <dimension ref="A1:AA57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1601,12 +1729,17 @@
     <col width="7" customWidth="1" style="68" min="18" max="18"/>
     <col width="7" customWidth="1" style="68" min="19" max="19"/>
     <col width="7" customWidth="1" style="68" min="20" max="20"/>
-    <col width="10" customWidth="1" style="68" min="21" max="21"/>
-    <col width="28" customWidth="1" style="68" min="22" max="22"/>
+    <col width="7" customWidth="1" style="68" min="21" max="21"/>
+    <col width="7" customWidth="1" style="68" min="22" max="22"/>
+    <col width="7" customWidth="1" style="68" min="23" max="23"/>
+    <col width="7" customWidth="1" style="68" min="24" max="24"/>
+    <col width="7" customWidth="1" style="68" min="25" max="25"/>
+    <col width="10" customWidth="1" style="68" min="26" max="26"/>
+    <col width="28" customWidth="1" style="68" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="116" t="inlineStr">
+      <c r="A1" s="122" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 설계팀 │ 2026</t>
         </is>
@@ -1631,10 +1764,15 @@
       <c r="S1" s="46" t="n"/>
       <c r="T1" s="46" t="n"/>
       <c r="U1" s="46" t="n"/>
-      <c r="V1" s="47" t="n"/>
+      <c r="V1" s="46" t="n"/>
+      <c r="W1" s="46" t="n"/>
+      <c r="X1" s="46" t="n"/>
+      <c r="Y1" s="46" t="n"/>
+      <c r="Z1" s="46" t="n"/>
+      <c r="AA1" s="47" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="117" t="inlineStr">
+      <c r="A2" s="123" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 설계팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1656,14 +1794,19 @@
       <c r="P2" s="46" t="n"/>
       <c r="Q2" s="46" t="n"/>
       <c r="R2" s="46" t="n"/>
-      <c r="S2" s="47" t="n"/>
-      <c r="T2" s="118" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 14:00</t>
-        </is>
-      </c>
+      <c r="S2" s="46" t="n"/>
+      <c r="T2" s="46" t="n"/>
       <c r="U2" s="46" t="n"/>
-      <c r="V2" s="47" t="n"/>
+      <c r="V2" s="46" t="n"/>
+      <c r="W2" s="46" t="n"/>
+      <c r="X2" s="47" t="n"/>
+      <c r="Y2" s="124" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 14:35</t>
+        </is>
+      </c>
+      <c r="Z2" s="46" t="n"/>
+      <c r="AA2" s="47" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="27" t="inlineStr">
@@ -1726,52 +1869,77 @@
           <t>✏입력</t>
         </is>
       </c>
-      <c r="M3" s="28" t="inlineStr">
+      <c r="M3" s="29" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="N3" s="28" t="inlineStr">
         <is>
           <t>✏입력</t>
         </is>
       </c>
-      <c r="N3" s="28" t="inlineStr">
+      <c r="O3" s="29" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="P3" s="28" t="inlineStr">
         <is>
           <t>✏입력</t>
         </is>
       </c>
-      <c r="O3" s="28" t="inlineStr">
+      <c r="Q3" s="29" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="R3" s="28" t="inlineStr">
         <is>
           <t>✏입력</t>
         </is>
       </c>
-      <c r="P3" s="28" t="inlineStr">
+      <c r="S3" s="29" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="T3" s="28" t="inlineStr">
         <is>
           <t>✏입력</t>
         </is>
       </c>
-      <c r="Q3" s="29" t="inlineStr">
+      <c r="U3" s="29" t="inlineStr">
         <is>
           <t>PO후입력</t>
         </is>
       </c>
-      <c r="R3" s="29" t="inlineStr">
+      <c r="V3" s="29" t="inlineStr">
         <is>
           <t>PO후입력</t>
         </is>
       </c>
-      <c r="S3" s="29" t="inlineStr">
+      <c r="W3" s="29" t="inlineStr">
         <is>
           <t>PO후입력</t>
         </is>
       </c>
-      <c r="T3" s="29" t="inlineStr">
+      <c r="X3" s="29" t="inlineStr">
         <is>
           <t>PO후입력</t>
         </is>
       </c>
-      <c r="U3" s="28" t="inlineStr">
+      <c r="Y3" s="29" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="Z3" s="28" t="inlineStr">
         <is>
           <t>✏선택▼</t>
         </is>
       </c>
-      <c r="V3" s="29" t="inlineStr">
+      <c r="AA3" s="29" t="inlineStr">
         <is>
           <t>✏메모</t>
         </is>
@@ -1839,59 +2007,84 @@
 컨셉</t>
         </is>
       </c>
-      <c r="M4" s="32" t="inlineStr">
+      <c r="M4" s="83" t="inlineStr">
+        <is>
+          <t>예정일</t>
+        </is>
+      </c>
+      <c r="N4" s="32" t="inlineStr">
         <is>
           <t>3D/2D
 설계</t>
         </is>
       </c>
-      <c r="N4" s="32" t="inlineStr">
+      <c r="O4" s="83" t="inlineStr">
+        <is>
+          <t>예정일</t>
+        </is>
+      </c>
+      <c r="P4" s="32" t="inlineStr">
         <is>
           <t>BOM
 작성</t>
         </is>
       </c>
-      <c r="O4" s="32" t="inlineStr">
+      <c r="Q4" s="83" t="inlineStr">
+        <is>
+          <t>예정일</t>
+        </is>
+      </c>
+      <c r="R4" s="32" t="inlineStr">
         <is>
           <t>가공품
 발주</t>
         </is>
       </c>
-      <c r="P4" s="32" t="inlineStr">
+      <c r="S4" s="83" t="inlineStr">
+        <is>
+          <t>예정일</t>
+        </is>
+      </c>
+      <c r="T4" s="32" t="inlineStr">
         <is>
           <t>메뉴얼</t>
         </is>
       </c>
-      <c r="Q4" s="83" t="inlineStr">
+      <c r="U4" s="83" t="inlineStr">
+        <is>
+          <t>예정일</t>
+        </is>
+      </c>
+      <c r="V4" s="83" t="inlineStr">
         <is>
           <t>제안서
 완료일</t>
         </is>
       </c>
-      <c r="R4" s="83" t="inlineStr">
+      <c r="W4" s="83" t="inlineStr">
         <is>
           <t>설계
 완료일</t>
         </is>
       </c>
-      <c r="S4" s="83" t="inlineStr">
+      <c r="X4" s="83" t="inlineStr">
         <is>
           <t>의뢰
 예정일</t>
         </is>
       </c>
-      <c r="T4" s="83" t="inlineStr">
+      <c r="Y4" s="83" t="inlineStr">
         <is>
           <t>의뢰
 입고일</t>
         </is>
       </c>
-      <c r="U4" s="32" t="inlineStr">
+      <c r="Z4" s="32" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="V4" s="32" t="inlineStr">
+      <c r="AA4" s="32" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1952,28 +2145,33 @@
       <c r="L5" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="M5" s="37" t="n">
-        <v>1</v>
-      </c>
+      <c r="M5" s="37" t="n"/>
       <c r="N5" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="O5" s="37" t="n">
+      <c r="O5" s="37" t="n"/>
+      <c r="P5" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="P5" s="37" t="n">
+      <c r="Q5" s="35" t="n"/>
+      <c r="R5" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" s="35" t="n"/>
+      <c r="T5" s="35" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q5" s="35" t="n"/>
-      <c r="R5" s="35" t="n"/>
-      <c r="S5" s="35" t="n"/>
-      <c r="T5" s="35" t="inlineStr">
+      <c r="U5" s="35" t="n"/>
+      <c r="V5" s="35" t="n"/>
+      <c r="W5" s="35" t="n"/>
+      <c r="X5" s="35" t="n"/>
+      <c r="Y5" s="35" t="inlineStr">
         <is>
           <t>진행중</t>
         </is>
       </c>
-      <c r="U5" s="35" t="n"/>
-      <c r="V5" s="38" t="n"/>
+      <c r="Z5" s="35" t="n"/>
+      <c r="AA5" s="38" t="n"/>
     </row>
     <row r="6" ht="22.05" customHeight="1">
       <c r="A6" s="39" t="n">
@@ -2026,28 +2224,33 @@
       <c r="L6" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="M6" s="43" t="n">
-        <v>1</v>
-      </c>
+      <c r="M6" s="43" t="n"/>
       <c r="N6" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="O6" s="43" t="n">
+      <c r="O6" s="43" t="n"/>
+      <c r="P6" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="41" t="n"/>
+      <c r="R6" s="41" t="n">
         <v>0.8</v>
       </c>
-      <c r="P6" s="43" t="n">
+      <c r="S6" s="41" t="n"/>
+      <c r="T6" s="41" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q6" s="41" t="n"/>
-      <c r="R6" s="41" t="n"/>
-      <c r="S6" s="41" t="n"/>
-      <c r="T6" s="41" t="inlineStr">
+      <c r="U6" s="41" t="n"/>
+      <c r="V6" s="41" t="n"/>
+      <c r="W6" s="41" t="n"/>
+      <c r="X6" s="41" t="n"/>
+      <c r="Y6" s="41" t="inlineStr">
         <is>
           <t>진행중</t>
         </is>
       </c>
-      <c r="U6" s="41" t="n"/>
-      <c r="V6" s="44" t="n"/>
+      <c r="Z6" s="41" t="n"/>
+      <c r="AA6" s="44" t="n"/>
     </row>
     <row r="7" ht="22.05" customHeight="1">
       <c r="A7" s="33" t="n">
@@ -2100,28 +2303,33 @@
       <c r="L7" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="M7" s="37" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="M7" s="37" t="n"/>
       <c r="N7" s="37" t="n">
         <v>0.5</v>
       </c>
-      <c r="O7" s="37" t="n">
+      <c r="O7" s="37" t="n"/>
+      <c r="P7" s="37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q7" s="35" t="n"/>
+      <c r="R7" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="P7" s="37" t="n">
+      <c r="S7" s="35" t="n"/>
+      <c r="T7" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" s="35" t="n"/>
-      <c r="R7" s="35" t="n"/>
-      <c r="S7" s="35" t="n"/>
-      <c r="T7" s="35" t="inlineStr">
+      <c r="U7" s="35" t="n"/>
+      <c r="V7" s="35" t="n"/>
+      <c r="W7" s="35" t="n"/>
+      <c r="X7" s="35" t="n"/>
+      <c r="Y7" s="35" t="inlineStr">
         <is>
           <t>진행중</t>
         </is>
       </c>
-      <c r="U7" s="35" t="n"/>
-      <c r="V7" s="38" t="n"/>
+      <c r="Z7" s="35" t="n"/>
+      <c r="AA7" s="38" t="n"/>
     </row>
     <row r="8" ht="22.05" customHeight="1">
       <c r="A8" s="39" t="n">
@@ -2181,7 +2389,12 @@
       <c r="S8" s="41" t="n"/>
       <c r="T8" s="41" t="n"/>
       <c r="U8" s="41" t="n"/>
-      <c r="V8" s="44" t="n"/>
+      <c r="V8" s="41" t="n"/>
+      <c r="W8" s="41" t="n"/>
+      <c r="X8" s="41" t="n"/>
+      <c r="Y8" s="41" t="n"/>
+      <c r="Z8" s="41" t="n"/>
+      <c r="AA8" s="44" t="n"/>
     </row>
     <row r="9" ht="22.05" customHeight="1">
       <c r="A9" s="33" t="n">
@@ -2243,7 +2456,12 @@
       <c r="S9" s="35" t="n"/>
       <c r="T9" s="35" t="n"/>
       <c r="U9" s="35" t="n"/>
-      <c r="V9" s="38" t="n"/>
+      <c r="V9" s="35" t="n"/>
+      <c r="W9" s="35" t="n"/>
+      <c r="X9" s="35" t="n"/>
+      <c r="Y9" s="35" t="n"/>
+      <c r="Z9" s="35" t="n"/>
+      <c r="AA9" s="38" t="n"/>
     </row>
     <row r="10" ht="22.05" customHeight="1">
       <c r="A10" s="39" t="n">
@@ -2303,7 +2521,12 @@
       <c r="S10" s="41" t="n"/>
       <c r="T10" s="41" t="n"/>
       <c r="U10" s="41" t="n"/>
-      <c r="V10" s="44" t="n"/>
+      <c r="V10" s="41" t="n"/>
+      <c r="W10" s="41" t="n"/>
+      <c r="X10" s="41" t="n"/>
+      <c r="Y10" s="41" t="n"/>
+      <c r="Z10" s="41" t="n"/>
+      <c r="AA10" s="44" t="n"/>
     </row>
     <row r="11" ht="22.05" customHeight="1">
       <c r="A11" s="33" t="n">
@@ -2365,7 +2588,12 @@
       <c r="S11" s="35" t="n"/>
       <c r="T11" s="35" t="n"/>
       <c r="U11" s="35" t="n"/>
-      <c r="V11" s="38" t="n"/>
+      <c r="V11" s="35" t="n"/>
+      <c r="W11" s="35" t="n"/>
+      <c r="X11" s="35" t="n"/>
+      <c r="Y11" s="35" t="n"/>
+      <c r="Z11" s="35" t="n"/>
+      <c r="AA11" s="38" t="n"/>
     </row>
     <row r="12" ht="22.05" customHeight="1">
       <c r="A12" s="39" t="n">
@@ -2427,7 +2655,12 @@
       <c r="S12" s="41" t="n"/>
       <c r="T12" s="41" t="n"/>
       <c r="U12" s="41" t="n"/>
-      <c r="V12" s="44" t="n"/>
+      <c r="V12" s="41" t="n"/>
+      <c r="W12" s="41" t="n"/>
+      <c r="X12" s="41" t="n"/>
+      <c r="Y12" s="41" t="n"/>
+      <c r="Z12" s="41" t="n"/>
+      <c r="AA12" s="44" t="n"/>
     </row>
     <row r="13" ht="22.05" customHeight="1">
       <c r="A13" s="33" t="n">
@@ -2487,7 +2720,12 @@
       <c r="S13" s="35" t="n"/>
       <c r="T13" s="35" t="n"/>
       <c r="U13" s="35" t="n"/>
-      <c r="V13" s="38" t="n"/>
+      <c r="V13" s="35" t="n"/>
+      <c r="W13" s="35" t="n"/>
+      <c r="X13" s="35" t="n"/>
+      <c r="Y13" s="35" t="n"/>
+      <c r="Z13" s="35" t="n"/>
+      <c r="AA13" s="38" t="n"/>
     </row>
     <row r="14" ht="22.05" customHeight="1">
       <c r="A14" s="39" t="n">
@@ -2549,7 +2787,12 @@
       <c r="S14" s="41" t="n"/>
       <c r="T14" s="41" t="n"/>
       <c r="U14" s="41" t="n"/>
-      <c r="V14" s="44" t="n"/>
+      <c r="V14" s="41" t="n"/>
+      <c r="W14" s="41" t="n"/>
+      <c r="X14" s="41" t="n"/>
+      <c r="Y14" s="41" t="n"/>
+      <c r="Z14" s="41" t="n"/>
+      <c r="AA14" s="44" t="n"/>
     </row>
     <row r="15" ht="22.05" customHeight="1">
       <c r="A15" s="33" t="n">
@@ -2611,7 +2854,12 @@
       <c r="S15" s="35" t="n"/>
       <c r="T15" s="35" t="n"/>
       <c r="U15" s="35" t="n"/>
-      <c r="V15" s="38" t="n"/>
+      <c r="V15" s="35" t="n"/>
+      <c r="W15" s="35" t="n"/>
+      <c r="X15" s="35" t="n"/>
+      <c r="Y15" s="35" t="n"/>
+      <c r="Z15" s="35" t="n"/>
+      <c r="AA15" s="38" t="n"/>
     </row>
     <row r="16" ht="22.05" customHeight="1">
       <c r="A16" s="39" t="n">
@@ -2677,7 +2925,12 @@
       <c r="S16" s="41" t="n"/>
       <c r="T16" s="41" t="n"/>
       <c r="U16" s="41" t="n"/>
-      <c r="V16" s="44" t="n"/>
+      <c r="V16" s="41" t="n"/>
+      <c r="W16" s="41" t="n"/>
+      <c r="X16" s="41" t="n"/>
+      <c r="Y16" s="41" t="n"/>
+      <c r="Z16" s="41" t="n"/>
+      <c r="AA16" s="44" t="n"/>
     </row>
     <row r="17" ht="22.05" customHeight="1">
       <c r="A17" s="33" t="n">
@@ -2743,7 +2996,12 @@
       <c r="S17" s="35" t="n"/>
       <c r="T17" s="35" t="n"/>
       <c r="U17" s="35" t="n"/>
-      <c r="V17" s="38" t="n"/>
+      <c r="V17" s="35" t="n"/>
+      <c r="W17" s="35" t="n"/>
+      <c r="X17" s="35" t="n"/>
+      <c r="Y17" s="35" t="n"/>
+      <c r="Z17" s="35" t="n"/>
+      <c r="AA17" s="38" t="n"/>
     </row>
     <row r="18" ht="22.05" customHeight="1">
       <c r="A18" s="39" t="n">
@@ -2805,7 +3063,12 @@
       <c r="S18" s="41" t="n"/>
       <c r="T18" s="41" t="n"/>
       <c r="U18" s="41" t="n"/>
-      <c r="V18" s="44" t="n"/>
+      <c r="V18" s="41" t="n"/>
+      <c r="W18" s="41" t="n"/>
+      <c r="X18" s="41" t="n"/>
+      <c r="Y18" s="41" t="n"/>
+      <c r="Z18" s="41" t="n"/>
+      <c r="AA18" s="44" t="n"/>
     </row>
     <row r="19" ht="22.05" customHeight="1">
       <c r="A19" s="33" t="n">
@@ -2867,7 +3130,12 @@
       <c r="S19" s="35" t="n"/>
       <c r="T19" s="35" t="n"/>
       <c r="U19" s="35" t="n"/>
-      <c r="V19" s="38" t="n"/>
+      <c r="V19" s="35" t="n"/>
+      <c r="W19" s="35" t="n"/>
+      <c r="X19" s="35" t="n"/>
+      <c r="Y19" s="35" t="n"/>
+      <c r="Z19" s="35" t="n"/>
+      <c r="AA19" s="38" t="n"/>
     </row>
     <row r="20" ht="22.05" customHeight="1">
       <c r="A20" s="39" t="n">
@@ -2929,7 +3197,12 @@
       <c r="S20" s="41" t="n"/>
       <c r="T20" s="41" t="n"/>
       <c r="U20" s="41" t="n"/>
-      <c r="V20" s="44" t="n"/>
+      <c r="V20" s="41" t="n"/>
+      <c r="W20" s="41" t="n"/>
+      <c r="X20" s="41" t="n"/>
+      <c r="Y20" s="41" t="n"/>
+      <c r="Z20" s="41" t="n"/>
+      <c r="AA20" s="44" t="n"/>
     </row>
     <row r="21" ht="22.05" customHeight="1">
       <c r="A21" s="33" t="n">
@@ -2991,7 +3264,12 @@
       <c r="S21" s="35" t="n"/>
       <c r="T21" s="35" t="n"/>
       <c r="U21" s="35" t="n"/>
-      <c r="V21" s="38" t="n"/>
+      <c r="V21" s="35" t="n"/>
+      <c r="W21" s="35" t="n"/>
+      <c r="X21" s="35" t="n"/>
+      <c r="Y21" s="35" t="n"/>
+      <c r="Z21" s="35" t="n"/>
+      <c r="AA21" s="38" t="n"/>
     </row>
     <row r="22" ht="22.05" customHeight="1">
       <c r="A22" s="39" t="n">
@@ -3053,7 +3331,12 @@
       <c r="S22" s="41" t="n"/>
       <c r="T22" s="41" t="n"/>
       <c r="U22" s="41" t="n"/>
-      <c r="V22" s="44" t="n"/>
+      <c r="V22" s="41" t="n"/>
+      <c r="W22" s="41" t="n"/>
+      <c r="X22" s="41" t="n"/>
+      <c r="Y22" s="41" t="n"/>
+      <c r="Z22" s="41" t="n"/>
+      <c r="AA22" s="44" t="n"/>
     </row>
     <row r="23" ht="22.05" customHeight="1">
       <c r="A23" s="33" t="n">
@@ -3115,7 +3398,12 @@
       <c r="S23" s="35" t="n"/>
       <c r="T23" s="35" t="n"/>
       <c r="U23" s="35" t="n"/>
-      <c r="V23" s="38" t="n"/>
+      <c r="V23" s="35" t="n"/>
+      <c r="W23" s="35" t="n"/>
+      <c r="X23" s="35" t="n"/>
+      <c r="Y23" s="35" t="n"/>
+      <c r="Z23" s="35" t="n"/>
+      <c r="AA23" s="38" t="n"/>
     </row>
     <row r="24" ht="22.05" customHeight="1">
       <c r="A24" s="39" t="n">
@@ -3177,7 +3465,12 @@
       <c r="S24" s="41" t="n"/>
       <c r="T24" s="41" t="n"/>
       <c r="U24" s="41" t="n"/>
-      <c r="V24" s="44" t="n"/>
+      <c r="V24" s="41" t="n"/>
+      <c r="W24" s="41" t="n"/>
+      <c r="X24" s="41" t="n"/>
+      <c r="Y24" s="41" t="n"/>
+      <c r="Z24" s="41" t="n"/>
+      <c r="AA24" s="44" t="n"/>
     </row>
     <row r="25" ht="22.05" customHeight="1">
       <c r="A25" s="33" t="n">
@@ -3239,7 +3532,12 @@
       <c r="S25" s="35" t="n"/>
       <c r="T25" s="35" t="n"/>
       <c r="U25" s="35" t="n"/>
-      <c r="V25" s="38" t="n"/>
+      <c r="V25" s="35" t="n"/>
+      <c r="W25" s="35" t="n"/>
+      <c r="X25" s="35" t="n"/>
+      <c r="Y25" s="35" t="n"/>
+      <c r="Z25" s="35" t="n"/>
+      <c r="AA25" s="38" t="n"/>
     </row>
     <row r="26" ht="22.05" customHeight="1">
       <c r="A26" s="39" t="n">
@@ -3301,7 +3599,12 @@
       <c r="S26" s="41" t="n"/>
       <c r="T26" s="41" t="n"/>
       <c r="U26" s="41" t="n"/>
-      <c r="V26" s="44" t="n"/>
+      <c r="V26" s="41" t="n"/>
+      <c r="W26" s="41" t="n"/>
+      <c r="X26" s="41" t="n"/>
+      <c r="Y26" s="41" t="n"/>
+      <c r="Z26" s="41" t="n"/>
+      <c r="AA26" s="44" t="n"/>
     </row>
     <row r="27" ht="22.05" customHeight="1">
       <c r="A27" s="33" t="n">
@@ -3363,7 +3666,12 @@
       <c r="S27" s="35" t="n"/>
       <c r="T27" s="35" t="n"/>
       <c r="U27" s="35" t="n"/>
-      <c r="V27" s="38" t="n"/>
+      <c r="V27" s="35" t="n"/>
+      <c r="W27" s="35" t="n"/>
+      <c r="X27" s="35" t="n"/>
+      <c r="Y27" s="35" t="n"/>
+      <c r="Z27" s="35" t="n"/>
+      <c r="AA27" s="38" t="n"/>
     </row>
     <row r="28" ht="22.05" customHeight="1">
       <c r="A28" s="39" t="n"/>
@@ -3387,7 +3695,12 @@
       <c r="S28" s="41" t="n"/>
       <c r="T28" s="41" t="n"/>
       <c r="U28" s="41" t="n"/>
-      <c r="V28" s="44" t="n"/>
+      <c r="V28" s="41" t="n"/>
+      <c r="W28" s="41" t="n"/>
+      <c r="X28" s="41" t="n"/>
+      <c r="Y28" s="41" t="n"/>
+      <c r="Z28" s="41" t="n"/>
+      <c r="AA28" s="44" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="33" t="n"/>
@@ -3411,7 +3724,12 @@
       <c r="S29" s="35" t="n"/>
       <c r="T29" s="35" t="n"/>
       <c r="U29" s="35" t="n"/>
-      <c r="V29" s="38" t="n"/>
+      <c r="V29" s="35" t="n"/>
+      <c r="W29" s="35" t="n"/>
+      <c r="X29" s="35" t="n"/>
+      <c r="Y29" s="35" t="n"/>
+      <c r="Z29" s="35" t="n"/>
+      <c r="AA29" s="38" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="39" t="n"/>
@@ -3435,7 +3753,12 @@
       <c r="S30" s="41" t="n"/>
       <c r="T30" s="41" t="n"/>
       <c r="U30" s="41" t="n"/>
-      <c r="V30" s="44" t="n"/>
+      <c r="V30" s="41" t="n"/>
+      <c r="W30" s="41" t="n"/>
+      <c r="X30" s="41" t="n"/>
+      <c r="Y30" s="41" t="n"/>
+      <c r="Z30" s="41" t="n"/>
+      <c r="AA30" s="44" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="33" t="n"/>
@@ -3459,7 +3782,12 @@
       <c r="S31" s="35" t="n"/>
       <c r="T31" s="35" t="n"/>
       <c r="U31" s="35" t="n"/>
-      <c r="V31" s="38" t="n"/>
+      <c r="V31" s="35" t="n"/>
+      <c r="W31" s="35" t="n"/>
+      <c r="X31" s="35" t="n"/>
+      <c r="Y31" s="35" t="n"/>
+      <c r="Z31" s="35" t="n"/>
+      <c r="AA31" s="38" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="39" t="n"/>
@@ -3483,7 +3811,12 @@
       <c r="S32" s="41" t="n"/>
       <c r="T32" s="41" t="n"/>
       <c r="U32" s="41" t="n"/>
-      <c r="V32" s="44" t="n"/>
+      <c r="V32" s="41" t="n"/>
+      <c r="W32" s="41" t="n"/>
+      <c r="X32" s="41" t="n"/>
+      <c r="Y32" s="41" t="n"/>
+      <c r="Z32" s="41" t="n"/>
+      <c r="AA32" s="44" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="33" t="n"/>
@@ -3507,7 +3840,12 @@
       <c r="S33" s="35" t="n"/>
       <c r="T33" s="35" t="n"/>
       <c r="U33" s="35" t="n"/>
-      <c r="V33" s="38" t="n"/>
+      <c r="V33" s="35" t="n"/>
+      <c r="W33" s="35" t="n"/>
+      <c r="X33" s="35" t="n"/>
+      <c r="Y33" s="35" t="n"/>
+      <c r="Z33" s="35" t="n"/>
+      <c r="AA33" s="38" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="39" t="n"/>
@@ -3531,7 +3869,12 @@
       <c r="S34" s="41" t="n"/>
       <c r="T34" s="41" t="n"/>
       <c r="U34" s="41" t="n"/>
-      <c r="V34" s="44" t="n"/>
+      <c r="V34" s="41" t="n"/>
+      <c r="W34" s="41" t="n"/>
+      <c r="X34" s="41" t="n"/>
+      <c r="Y34" s="41" t="n"/>
+      <c r="Z34" s="41" t="n"/>
+      <c r="AA34" s="44" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="33" t="n"/>
@@ -3555,7 +3898,12 @@
       <c r="S35" s="35" t="n"/>
       <c r="T35" s="35" t="n"/>
       <c r="U35" s="35" t="n"/>
-      <c r="V35" s="38" t="n"/>
+      <c r="V35" s="35" t="n"/>
+      <c r="W35" s="35" t="n"/>
+      <c r="X35" s="35" t="n"/>
+      <c r="Y35" s="35" t="n"/>
+      <c r="Z35" s="35" t="n"/>
+      <c r="AA35" s="38" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="39" t="n"/>
@@ -3579,7 +3927,12 @@
       <c r="S36" s="41" t="n"/>
       <c r="T36" s="41" t="n"/>
       <c r="U36" s="41" t="n"/>
-      <c r="V36" s="44" t="n"/>
+      <c r="V36" s="41" t="n"/>
+      <c r="W36" s="41" t="n"/>
+      <c r="X36" s="41" t="n"/>
+      <c r="Y36" s="41" t="n"/>
+      <c r="Z36" s="41" t="n"/>
+      <c r="AA36" s="44" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="33" t="n"/>
@@ -3603,7 +3956,12 @@
       <c r="S37" s="35" t="n"/>
       <c r="T37" s="35" t="n"/>
       <c r="U37" s="35" t="n"/>
-      <c r="V37" s="38" t="n"/>
+      <c r="V37" s="35" t="n"/>
+      <c r="W37" s="35" t="n"/>
+      <c r="X37" s="35" t="n"/>
+      <c r="Y37" s="35" t="n"/>
+      <c r="Z37" s="35" t="n"/>
+      <c r="AA37" s="38" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="39" t="n"/>
@@ -3627,7 +3985,12 @@
       <c r="S38" s="41" t="n"/>
       <c r="T38" s="41" t="n"/>
       <c r="U38" s="41" t="n"/>
-      <c r="V38" s="44" t="n"/>
+      <c r="V38" s="41" t="n"/>
+      <c r="W38" s="41" t="n"/>
+      <c r="X38" s="41" t="n"/>
+      <c r="Y38" s="41" t="n"/>
+      <c r="Z38" s="41" t="n"/>
+      <c r="AA38" s="44" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="33" t="n"/>
@@ -3651,7 +4014,12 @@
       <c r="S39" s="35" t="n"/>
       <c r="T39" s="35" t="n"/>
       <c r="U39" s="35" t="n"/>
-      <c r="V39" s="38" t="n"/>
+      <c r="V39" s="35" t="n"/>
+      <c r="W39" s="35" t="n"/>
+      <c r="X39" s="35" t="n"/>
+      <c r="Y39" s="35" t="n"/>
+      <c r="Z39" s="35" t="n"/>
+      <c r="AA39" s="38" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="39" t="n"/>
@@ -3675,7 +4043,12 @@
       <c r="S40" s="41" t="n"/>
       <c r="T40" s="41" t="n"/>
       <c r="U40" s="41" t="n"/>
-      <c r="V40" s="44" t="n"/>
+      <c r="V40" s="41" t="n"/>
+      <c r="W40" s="41" t="n"/>
+      <c r="X40" s="41" t="n"/>
+      <c r="Y40" s="41" t="n"/>
+      <c r="Z40" s="41" t="n"/>
+      <c r="AA40" s="44" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="33" t="n"/>
@@ -3699,7 +4072,12 @@
       <c r="S41" s="35" t="n"/>
       <c r="T41" s="35" t="n"/>
       <c r="U41" s="35" t="n"/>
-      <c r="V41" s="38" t="n"/>
+      <c r="V41" s="35" t="n"/>
+      <c r="W41" s="35" t="n"/>
+      <c r="X41" s="35" t="n"/>
+      <c r="Y41" s="35" t="n"/>
+      <c r="Z41" s="35" t="n"/>
+      <c r="AA41" s="38" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="39" t="n"/>
@@ -3723,7 +4101,12 @@
       <c r="S42" s="41" t="n"/>
       <c r="T42" s="41" t="n"/>
       <c r="U42" s="41" t="n"/>
-      <c r="V42" s="44" t="n"/>
+      <c r="V42" s="41" t="n"/>
+      <c r="W42" s="41" t="n"/>
+      <c r="X42" s="41" t="n"/>
+      <c r="Y42" s="41" t="n"/>
+      <c r="Z42" s="41" t="n"/>
+      <c r="AA42" s="44" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="33" t="n"/>
@@ -3747,7 +4130,12 @@
       <c r="S43" s="35" t="n"/>
       <c r="T43" s="35" t="n"/>
       <c r="U43" s="35" t="n"/>
-      <c r="V43" s="38" t="n"/>
+      <c r="V43" s="35" t="n"/>
+      <c r="W43" s="35" t="n"/>
+      <c r="X43" s="35" t="n"/>
+      <c r="Y43" s="35" t="n"/>
+      <c r="Z43" s="35" t="n"/>
+      <c r="AA43" s="38" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="39" t="n"/>
@@ -3771,7 +4159,12 @@
       <c r="S44" s="41" t="n"/>
       <c r="T44" s="41" t="n"/>
       <c r="U44" s="41" t="n"/>
-      <c r="V44" s="44" t="n"/>
+      <c r="V44" s="41" t="n"/>
+      <c r="W44" s="41" t="n"/>
+      <c r="X44" s="41" t="n"/>
+      <c r="Y44" s="41" t="n"/>
+      <c r="Z44" s="41" t="n"/>
+      <c r="AA44" s="44" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="33" t="n"/>
@@ -3795,7 +4188,12 @@
       <c r="S45" s="35" t="n"/>
       <c r="T45" s="35" t="n"/>
       <c r="U45" s="35" t="n"/>
-      <c r="V45" s="38" t="n"/>
+      <c r="V45" s="35" t="n"/>
+      <c r="W45" s="35" t="n"/>
+      <c r="X45" s="35" t="n"/>
+      <c r="Y45" s="35" t="n"/>
+      <c r="Z45" s="35" t="n"/>
+      <c r="AA45" s="38" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="39" t="n"/>
@@ -3819,7 +4217,12 @@
       <c r="S46" s="41" t="n"/>
       <c r="T46" s="41" t="n"/>
       <c r="U46" s="41" t="n"/>
-      <c r="V46" s="44" t="n"/>
+      <c r="V46" s="41" t="n"/>
+      <c r="W46" s="41" t="n"/>
+      <c r="X46" s="41" t="n"/>
+      <c r="Y46" s="41" t="n"/>
+      <c r="Z46" s="41" t="n"/>
+      <c r="AA46" s="44" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="33" t="n"/>
@@ -3843,7 +4246,12 @@
       <c r="S47" s="35" t="n"/>
       <c r="T47" s="35" t="n"/>
       <c r="U47" s="35" t="n"/>
-      <c r="V47" s="38" t="n"/>
+      <c r="V47" s="35" t="n"/>
+      <c r="W47" s="35" t="n"/>
+      <c r="X47" s="35" t="n"/>
+      <c r="Y47" s="35" t="n"/>
+      <c r="Z47" s="35" t="n"/>
+      <c r="AA47" s="38" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="39" t="n"/>
@@ -3867,7 +4275,12 @@
       <c r="S48" s="41" t="n"/>
       <c r="T48" s="41" t="n"/>
       <c r="U48" s="41" t="n"/>
-      <c r="V48" s="44" t="n"/>
+      <c r="V48" s="41" t="n"/>
+      <c r="W48" s="41" t="n"/>
+      <c r="X48" s="41" t="n"/>
+      <c r="Y48" s="41" t="n"/>
+      <c r="Z48" s="41" t="n"/>
+      <c r="AA48" s="44" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="33" t="n"/>
@@ -3891,7 +4304,12 @@
       <c r="S49" s="35" t="n"/>
       <c r="T49" s="35" t="n"/>
       <c r="U49" s="35" t="n"/>
-      <c r="V49" s="38" t="n"/>
+      <c r="V49" s="35" t="n"/>
+      <c r="W49" s="35" t="n"/>
+      <c r="X49" s="35" t="n"/>
+      <c r="Y49" s="35" t="n"/>
+      <c r="Z49" s="35" t="n"/>
+      <c r="AA49" s="38" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="39" t="n"/>
@@ -3915,7 +4333,12 @@
       <c r="S50" s="41" t="n"/>
       <c r="T50" s="41" t="n"/>
       <c r="U50" s="41" t="n"/>
-      <c r="V50" s="44" t="n"/>
+      <c r="V50" s="41" t="n"/>
+      <c r="W50" s="41" t="n"/>
+      <c r="X50" s="41" t="n"/>
+      <c r="Y50" s="41" t="n"/>
+      <c r="Z50" s="41" t="n"/>
+      <c r="AA50" s="44" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="33" t="n"/>
@@ -3939,7 +4362,12 @@
       <c r="S51" s="35" t="n"/>
       <c r="T51" s="35" t="n"/>
       <c r="U51" s="35" t="n"/>
-      <c r="V51" s="38" t="n"/>
+      <c r="V51" s="35" t="n"/>
+      <c r="W51" s="35" t="n"/>
+      <c r="X51" s="35" t="n"/>
+      <c r="Y51" s="35" t="n"/>
+      <c r="Z51" s="35" t="n"/>
+      <c r="AA51" s="38" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="39" t="n"/>
@@ -3963,7 +4391,12 @@
       <c r="S52" s="41" t="n"/>
       <c r="T52" s="41" t="n"/>
       <c r="U52" s="41" t="n"/>
-      <c r="V52" s="44" t="n"/>
+      <c r="V52" s="41" t="n"/>
+      <c r="W52" s="41" t="n"/>
+      <c r="X52" s="41" t="n"/>
+      <c r="Y52" s="41" t="n"/>
+      <c r="Z52" s="41" t="n"/>
+      <c r="AA52" s="44" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="33" t="n"/>
@@ -3987,7 +4420,12 @@
       <c r="S53" s="35" t="n"/>
       <c r="T53" s="35" t="n"/>
       <c r="U53" s="35" t="n"/>
-      <c r="V53" s="38" t="n"/>
+      <c r="V53" s="35" t="n"/>
+      <c r="W53" s="35" t="n"/>
+      <c r="X53" s="35" t="n"/>
+      <c r="Y53" s="35" t="n"/>
+      <c r="Z53" s="35" t="n"/>
+      <c r="AA53" s="38" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="39" t="n"/>
@@ -4011,7 +4449,12 @@
       <c r="S54" s="41" t="n"/>
       <c r="T54" s="41" t="n"/>
       <c r="U54" s="41" t="n"/>
-      <c r="V54" s="44" t="n"/>
+      <c r="V54" s="41" t="n"/>
+      <c r="W54" s="41" t="n"/>
+      <c r="X54" s="41" t="n"/>
+      <c r="Y54" s="41" t="n"/>
+      <c r="Z54" s="41" t="n"/>
+      <c r="AA54" s="44" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="33" t="n"/>
@@ -4035,7 +4478,12 @@
       <c r="S55" s="35" t="n"/>
       <c r="T55" s="35" t="n"/>
       <c r="U55" s="35" t="n"/>
-      <c r="V55" s="38" t="n"/>
+      <c r="V55" s="35" t="n"/>
+      <c r="W55" s="35" t="n"/>
+      <c r="X55" s="35" t="n"/>
+      <c r="Y55" s="35" t="n"/>
+      <c r="Z55" s="35" t="n"/>
+      <c r="AA55" s="38" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="39" t="n"/>
@@ -4059,7 +4507,12 @@
       <c r="S56" s="41" t="n"/>
       <c r="T56" s="41" t="n"/>
       <c r="U56" s="41" t="n"/>
-      <c r="V56" s="44" t="n"/>
+      <c r="V56" s="41" t="n"/>
+      <c r="W56" s="41" t="n"/>
+      <c r="X56" s="41" t="n"/>
+      <c r="Y56" s="41" t="n"/>
+      <c r="Z56" s="41" t="n"/>
+      <c r="AA56" s="44" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="33" t="n"/>
@@ -4083,14 +4536,19 @@
       <c r="S57" s="35" t="n"/>
       <c r="T57" s="35" t="n"/>
       <c r="U57" s="35" t="n"/>
-      <c r="V57" s="38" t="n"/>
+      <c r="V57" s="35" t="n"/>
+      <c r="W57" s="35" t="n"/>
+      <c r="X57" s="35" t="n"/>
+      <c r="Y57" s="35" t="n"/>
+      <c r="Z57" s="35" t="n"/>
+      <c r="AA57" s="38" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="3">
-    <mergeCell ref="T2:V2"/>
-    <mergeCell ref="A1:V1"/>
-    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A1:AA1"/>
+    <mergeCell ref="A2:X2"/>
+    <mergeCell ref="Y2:AA2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="Q5:Q28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_설계팀_입력_2026.xlsx
@@ -118,7 +118,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -218,6 +218,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00B08F36"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000277BD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF6C00"/>
       </patternFill>
     </fill>
   </fills>
@@ -393,7 +403,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -766,6 +776,21 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1739,7 +1764,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="122" t="inlineStr">
+      <c r="A1" s="125" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 설계팀 │ 2026</t>
         </is>
@@ -1772,7 +1797,7 @@
       <c r="AA1" s="47" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="123" t="inlineStr">
+      <c r="A2" s="126" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 설계팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1800,9 +1825,9 @@
       <c r="V2" s="46" t="n"/>
       <c r="W2" s="46" t="n"/>
       <c r="X2" s="47" t="n"/>
-      <c r="Y2" s="124" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 14:35</t>
+      <c r="Y2" s="127" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 15:15</t>
         </is>
       </c>
       <c r="Z2" s="46" t="n"/>
@@ -2001,56 +2026,56 @@
           <t>부서진척률(%)</t>
         </is>
       </c>
-      <c r="L4" s="32" t="inlineStr">
+      <c r="L4" s="128" t="inlineStr">
         <is>
           <t>상세
 컨셉</t>
         </is>
       </c>
-      <c r="M4" s="83" t="inlineStr">
+      <c r="M4" s="128" t="inlineStr">
         <is>
           <t>예정일</t>
         </is>
       </c>
-      <c r="N4" s="32" t="inlineStr">
+      <c r="N4" s="129" t="inlineStr">
         <is>
           <t>3D/2D
 설계</t>
         </is>
       </c>
-      <c r="O4" s="83" t="inlineStr">
+      <c r="O4" s="129" t="inlineStr">
         <is>
           <t>예정일</t>
         </is>
       </c>
-      <c r="P4" s="32" t="inlineStr">
+      <c r="P4" s="128" t="inlineStr">
         <is>
           <t>BOM
 작성</t>
         </is>
       </c>
-      <c r="Q4" s="83" t="inlineStr">
+      <c r="Q4" s="128" t="inlineStr">
         <is>
           <t>예정일</t>
         </is>
       </c>
-      <c r="R4" s="32" t="inlineStr">
+      <c r="R4" s="129" t="inlineStr">
         <is>
           <t>가공품
 발주</t>
         </is>
       </c>
-      <c r="S4" s="83" t="inlineStr">
+      <c r="S4" s="129" t="inlineStr">
         <is>
           <t>예정일</t>
         </is>
       </c>
-      <c r="T4" s="32" t="inlineStr">
+      <c r="T4" s="128" t="inlineStr">
         <is>
           <t>메뉴얼</t>
         </is>
       </c>
-      <c r="U4" s="83" t="inlineStr">
+      <c r="U4" s="128" t="inlineStr">
         <is>
           <t>예정일</t>
         </is>
